--- a/languages/pt/output/import/葡萄牙语专四进阶.xlsx
+++ b/languages/pt/output/import/葡萄牙语专四进阶.xlsx
@@ -45835,7 +45835,7 @@
       </c>
       <c r="B1422" s="1" t="inlineStr">
         <is>
-          <t>[ˌpeˈte] zh&lt;名&gt;</t>
+          <t>[ˌpeˈte] 葡萄牙语；巴西劳工党&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1422" s="1" t="inlineStr">
@@ -45845,7 +45845,7 @@
       </c>
       <c r="D1422" s="1" t="inlineStr">
         <is>
-          <t>zh</t>
+          <t>葡萄牙语</t>
         </is>
       </c>
       <c r="E1422" s="1" t="inlineStr">
@@ -75895,13 +75895,13 @@
       </c>
       <c r="B2364" s="1" t="inlineStr">
         <is>
-          <t>SS&lt;名&gt;</t>
+          <t>党卫军；党卫队&lt;名&gt;</t>
         </is>
       </c>
       <c r="C2364" s="1" t="inlineStr"/>
       <c r="D2364" s="1" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>党卫军</t>
         </is>
       </c>
       <c r="E2364" s="1" t="inlineStr">

--- a/languages/pt/output/import/葡萄牙语专四进阶.xlsx
+++ b/languages/pt/output/import/葡萄牙语专四进阶.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="词汇表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="词汇表" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>[veˈʎɔ.t͡ʃi] 老人&lt;名&gt;</t>
+          <t>[/veˈʎɔ.t͡ʃi/] 老头；老汉&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>老人</t>
+          <t>老头；老汉</t>
         </is>
       </c>
       <c r="E7" s="1" t="inlineStr">
@@ -691,17 +691,17 @@
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>[ˈa] 哈&lt;动&gt;</t>
+          <t>[ˈa] 有；存在；……以前&lt;动&gt;</t>
         </is>
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>ˈa</t>
+          <t>/ˈa/</t>
         </is>
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>哈</t>
+          <t>有；存在；……以前</t>
         </is>
       </c>
       <c r="E9" s="1" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t>[kõ.deˈna.du] 谴责&lt;名&gt;</t>
+          <t>[kõ.deˈna.du] 被判刑的；被定罪的；罪犯&lt;名&gt;</t>
         </is>
       </c>
       <c r="C41" s="1" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="D41" s="1" t="inlineStr">
         <is>
-          <t>谴责</t>
+          <t>被判刑的；被定罪的；罪犯</t>
         </is>
       </c>
       <c r="E41" s="1" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="B46" s="1" t="inlineStr">
         <is>
-          <t>[kõ.pe.t͡ʃiˈsɐ̃w̃] 竞争&lt;名&gt;</t>
+          <t>[/kõ.pe.t͡ʃiˈsɐ̃w̃/] 竞赛；比赛；竞争&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C46" s="1" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="D46" s="1" t="inlineStr">
         <is>
-          <t>竞争</t>
+          <t>竞赛；比赛；竞争&lt;名&gt;</t>
         </is>
       </c>
       <c r="E46" s="1" t="inlineStr">
@@ -2419,7 +2419,7 @@
       </c>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t>[kõ.takˈta(ʁ)] 联系方式&lt;动&gt;</t>
+          <t>[kõ.takˈta(ʁ)] 联系；联络&lt;动&gt;</t>
         </is>
       </c>
       <c r="C63" s="1" t="inlineStr">
@@ -2429,7 +2429,7 @@
       </c>
       <c r="D63" s="1" t="inlineStr">
         <is>
-          <t>联系方式</t>
+          <t>联系；联络</t>
         </is>
       </c>
       <c r="E63" s="1" t="inlineStr">
@@ -2515,13 +2515,17 @@
       </c>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t>检查员&lt;名&gt;</t>
-        </is>
-      </c>
-      <c r="C66" s="1" t="inlineStr"/>
+          <t>[[ĩspɨkˈtoɾ]] 检查员&lt;名&gt;（旧拼写，现规范为 inspetor）&lt;noun&gt;</t>
+        </is>
+      </c>
+      <c r="C66" s="1" t="inlineStr">
+        <is>
+          <t>/ĩs.pɛkˈto(ʁ)/</t>
+        </is>
+      </c>
       <c r="D66" s="1" t="inlineStr">
         <is>
-          <t>检查员</t>
+          <t>检查员&lt;名&gt;（旧拼写，现规范为 inspetor）</t>
         </is>
       </c>
       <c r="E66" s="1" t="inlineStr">
@@ -2804,7 +2808,7 @@
       </c>
       <c r="C75" s="1" t="inlineStr">
         <is>
-          <t>tẽ.ˈta.ɾãʊ̃</t>
+          <t>/tẽ.ˈta.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D75" s="1" t="inlineStr">
@@ -2831,7 +2835,7 @@
       </c>
       <c r="B76" s="1" t="inlineStr">
         <is>
-          <t>[ĩ.feˈlis] 不高兴&lt;形&gt;</t>
+          <t>[/ĩ.feˈlis/] 不幸的；不快乐的&lt;形&gt;&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C76" s="1" t="inlineStr">
@@ -2841,7 +2845,7 @@
       </c>
       <c r="D76" s="1" t="inlineStr">
         <is>
-          <t>不高兴</t>
+          <t>不幸的；不快乐的&lt;形&gt;</t>
         </is>
       </c>
       <c r="E76" s="1" t="inlineStr">
@@ -2895,7 +2899,7 @@
       </c>
       <c r="B78" s="1" t="inlineStr">
         <is>
-          <t>[vi.ʒiˈa(ʁ)] 手表&lt;动&gt;</t>
+          <t>[vi.ʒiˈa(ʁ)] 监视；看守；警戒&lt;动&gt;</t>
         </is>
       </c>
       <c r="C78" s="1" t="inlineStr">
@@ -2905,7 +2909,7 @@
       </c>
       <c r="D78" s="1" t="inlineStr">
         <is>
-          <t>手表</t>
+          <t>监视；看守；警戒</t>
         </is>
       </c>
       <c r="E78" s="1" t="inlineStr">
@@ -2959,7 +2963,7 @@
       </c>
       <c r="B80" s="1" t="inlineStr">
         <is>
-          <t>[ˈpi.lɐ] 迪克&lt;名&gt;</t>
+          <t>[ˈpi.lɐ] 阴茎（俚语）；钱（巴西俚语）&lt;名&gt;</t>
         </is>
       </c>
       <c r="C80" s="1" t="inlineStr">
@@ -2969,7 +2973,7 @@
       </c>
       <c r="D80" s="1" t="inlineStr">
         <is>
-          <t>迪克</t>
+          <t>阴茎（俚语）；钱（巴西俚语）</t>
         </is>
       </c>
       <c r="E80" s="1" t="inlineStr">
@@ -3215,7 +3219,7 @@
       </c>
       <c r="B88" s="1" t="inlineStr">
         <is>
-          <t>[ˈda.dɐ] 给定&lt;名&gt;</t>
+          <t>[/ˈda.dɐ/] dar的阴性过去分词；给定的&lt;形&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C88" s="1" t="inlineStr">
@@ -3225,7 +3229,7 @@
       </c>
       <c r="D88" s="1" t="inlineStr">
         <is>
-          <t>给定</t>
+          <t>dar的阴性过去分词；给定的&lt;形&gt;</t>
         </is>
       </c>
       <c r="E88" s="1" t="inlineStr">
@@ -3247,7 +3251,7 @@
       </c>
       <c r="B89" s="1" t="inlineStr">
         <is>
-          <t>[ˈbɾĩ.d͡ʒi] 吐司&lt;名&gt;</t>
+          <t>[ˈbɾĩ.d͡ʒi] 祝酒；干杯；赠品&lt;名&gt;</t>
         </is>
       </c>
       <c r="C89" s="1" t="inlineStr">
@@ -3257,7 +3261,7 @@
       </c>
       <c r="D89" s="1" t="inlineStr">
         <is>
-          <t>吐司</t>
+          <t>祝酒；干杯；赠品</t>
         </is>
       </c>
       <c r="E89" s="1" t="inlineStr">
@@ -3316,7 +3320,7 @@
       </c>
       <c r="C91" s="1" t="inlineStr">
         <is>
-          <t>es.pɛ.ta.ku.ˈlax</t>
+          <t>/es.pɛ.ta.ku.ˈlax/</t>
         </is>
       </c>
       <c r="D91" s="1" t="inlineStr">
@@ -3535,17 +3539,17 @@
       </c>
       <c r="B98" s="1" t="inlineStr">
         <is>
-          <t>[ej dʒi] 嘿&lt;动&gt;</t>
+          <t>[ej dʒi] 必须；必定会&lt;动&gt;</t>
         </is>
       </c>
       <c r="C98" s="1" t="inlineStr">
         <is>
-          <t>ej dʒi</t>
+          <t>/ej dʒi/</t>
         </is>
       </c>
       <c r="D98" s="1" t="inlineStr">
         <is>
-          <t>嘿</t>
+          <t>必须；必定会</t>
         </is>
       </c>
       <c r="E98" s="1" t="inlineStr">
@@ -4047,7 +4051,7 @@
       </c>
       <c r="B114" s="1" t="inlineStr">
         <is>
-          <t>[des.kõ.ɲeˈsi.du] 未知&lt;名&gt;</t>
+          <t>[/des.kõ.ɲeˈsi.du/] 未知的&lt;形&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C114" s="1" t="inlineStr">
@@ -4057,7 +4061,7 @@
       </c>
       <c r="D114" s="1" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>未知的&lt;形&gt;</t>
         </is>
       </c>
       <c r="E114" s="1" t="inlineStr">
@@ -4788,7 +4792,7 @@
       </c>
       <c r="C137" s="1" t="inlineStr">
         <is>
-          <t>xe.a.ˈsãʊ̃</t>
+          <t>/xe.a.ˈsãʊ̃/</t>
         </is>
       </c>
       <c r="D137" s="1" t="inlineStr">
@@ -4847,17 +4851,17 @@
       </c>
       <c r="B139" s="1" t="inlineStr">
         <is>
-          <t>[sa.ˈi.ɾãʊ̃] 左&lt;动&gt;</t>
+          <t>[sa.ˈi.ɾãʊ̃] 离开；出去&lt;动&gt;</t>
         </is>
       </c>
       <c r="C139" s="1" t="inlineStr">
         <is>
-          <t>sa.ˈi.ɾãʊ̃</t>
+          <t>/sa.ˈi.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D139" s="1" t="inlineStr">
         <is>
-          <t>左</t>
+          <t>离开；出去</t>
         </is>
       </c>
       <c r="E139" s="1" t="inlineStr">
@@ -5007,7 +5011,7 @@
       </c>
       <c r="B144" s="1" t="inlineStr">
         <is>
-          <t>[ˈsaw.vɐ] 萨尔瓦&lt;名&gt;</t>
+          <t>[ˈsaw.vɐ] 礼炮；一阵掌声&lt;名&gt;</t>
         </is>
       </c>
       <c r="C144" s="1" t="inlineStr">
@@ -5017,7 +5021,7 @@
       </c>
       <c r="D144" s="1" t="inlineStr">
         <is>
-          <t>萨尔瓦</t>
+          <t>礼炮；一阵掌声</t>
         </is>
       </c>
       <c r="E144" s="1" t="inlineStr">
@@ -5039,7 +5043,7 @@
       </c>
       <c r="B145" s="1" t="inlineStr">
         <is>
-          <t>[d͡ʒis.paˈɾa.t͡ʃi] 废话&lt;名&gt;</t>
+          <t>[d͡ʒis.paˈɾa.t͡ʃi] 胡话；荒谬；蠢事&lt;名&gt;</t>
         </is>
       </c>
       <c r="C145" s="1" t="inlineStr">
@@ -5049,7 +5053,7 @@
       </c>
       <c r="D145" s="1" t="inlineStr">
         <is>
-          <t>废话</t>
+          <t>胡话；荒谬；蠢事</t>
         </is>
       </c>
       <c r="E145" s="1" t="inlineStr">
@@ -5103,7 +5107,7 @@
       </c>
       <c r="B147" s="1" t="inlineStr">
         <is>
-          <t>[ˈpaws] 迪克斯&lt;名&gt;</t>
+          <t>[ˈpaws] 棍；棒；木棍&lt;名&gt;</t>
         </is>
       </c>
       <c r="C147" s="1" t="inlineStr">
@@ -5113,7 +5117,7 @@
       </c>
       <c r="D147" s="1" t="inlineStr">
         <is>
-          <t>迪克斯</t>
+          <t>棍；棒；木棍</t>
         </is>
       </c>
       <c r="E147" s="1" t="inlineStr">
@@ -5231,7 +5235,7 @@
       </c>
       <c r="B151" s="1" t="inlineStr">
         <is>
-          <t>[moˈɾa(ʁ)] 直播&lt;动&gt;</t>
+          <t>[moˈɾa(ʁ)] 居住&lt;动&gt;</t>
         </is>
       </c>
       <c r="C151" s="1" t="inlineStr">
@@ -5241,7 +5245,7 @@
       </c>
       <c r="D151" s="1" t="inlineStr">
         <is>
-          <t>直播</t>
+          <t>居住</t>
         </is>
       </c>
       <c r="E151" s="1" t="inlineStr">
@@ -5519,7 +5523,7 @@
       </c>
       <c r="B160" s="1" t="inlineStr">
         <is>
-          <t>[no.viˈda.d͡ʒi] 新的&lt;名&gt;</t>
+          <t>[no.viˈda.d͡ʒi] 新闻；新鲜事；新事物&lt;名&gt;</t>
         </is>
       </c>
       <c r="C160" s="1" t="inlineStr">
@@ -5529,7 +5533,7 @@
       </c>
       <c r="D160" s="1" t="inlineStr">
         <is>
-          <t>新的</t>
+          <t>新闻；新鲜事；新事物</t>
         </is>
       </c>
       <c r="E160" s="1" t="inlineStr">
@@ -5839,7 +5843,7 @@
       </c>
       <c r="B170" s="1" t="inlineStr">
         <is>
-          <t>[ˈʁaw.zi] 房子&lt;名&gt;</t>
+          <t>[/ˈʁaw.zi/] 豪斯音乐（一种电子舞曲）&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C170" s="1" t="inlineStr">
@@ -5849,7 +5853,7 @@
       </c>
       <c r="D170" s="1" t="inlineStr">
         <is>
-          <t>房子</t>
+          <t>豪斯音乐（一种电子舞曲）&lt;名&gt;</t>
         </is>
       </c>
       <c r="E170" s="1" t="inlineStr">
@@ -6127,7 +6131,7 @@
       </c>
       <c r="B179" s="1" t="inlineStr">
         <is>
-          <t>[ʒuwˈɡa(ʁ)] 法官&lt;动&gt;</t>
+          <t>[ʒuwˈɡa(ʁ)] 审判；判断；认为&lt;动&gt;</t>
         </is>
       </c>
       <c r="C179" s="1" t="inlineStr">
@@ -6137,7 +6141,7 @@
       </c>
       <c r="D179" s="1" t="inlineStr">
         <is>
-          <t>法官</t>
+          <t>审判；判断；认为</t>
         </is>
       </c>
       <c r="E179" s="1" t="inlineStr">
@@ -6159,7 +6163,7 @@
       </c>
       <c r="B180" s="1" t="inlineStr">
         <is>
-          <t>[ˈvi.ɾɐ] 转&lt;名&gt;</t>
+          <t>[/ˈvi.ɾɐ/] virar的动词变位（转）&lt;动&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C180" s="1" t="inlineStr">
@@ -6169,7 +6173,7 @@
       </c>
       <c r="D180" s="1" t="inlineStr">
         <is>
-          <t>转</t>
+          <t>virar的动词变位（转）&lt;动&gt;</t>
         </is>
       </c>
       <c r="E180" s="1" t="inlineStr">
@@ -6191,13 +6195,17 @@
       </c>
       <c r="B181" s="1" t="inlineStr">
         <is>
-          <t>家庭&lt;名&gt;</t>
-        </is>
-      </c>
-      <c r="C181" s="1" t="inlineStr"/>
+          <t>[[fɐˈmiljɐ]] família 家庭&lt;名&gt;&lt;noun&gt;</t>
+        </is>
+      </c>
+      <c r="C181" s="1" t="inlineStr">
+        <is>
+          <t>/fa.ˈmi.ʎu/</t>
+        </is>
+      </c>
       <c r="D181" s="1" t="inlineStr">
         <is>
-          <t>家庭</t>
+          <t>família 家庭&lt;名&gt;</t>
         </is>
       </c>
       <c r="E181" s="1" t="inlineStr">
@@ -6219,7 +6227,7 @@
       </c>
       <c r="B182" s="1" t="inlineStr">
         <is>
-          <t>[aˈɛ.ɾju] 天线&lt;形&gt;</t>
+          <t>[aˈɛ.ɾju] 空中的；航空的&lt;形&gt;</t>
         </is>
       </c>
       <c r="C182" s="1" t="inlineStr">
@@ -6229,7 +6237,7 @@
       </c>
       <c r="D182" s="1" t="inlineStr">
         <is>
-          <t>天线</t>
+          <t>空中的；航空的</t>
         </is>
       </c>
       <c r="E182" s="1" t="inlineStr">
@@ -6827,7 +6835,7 @@
       </c>
       <c r="B201" s="1" t="inlineStr">
         <is>
-          <t>[ˈpɾĩ.mɐ] 表弟&lt;形&gt;</t>
+          <t>[ˈpɾĩ.mɐ] 表姐；表妹&lt;形&gt;</t>
         </is>
       </c>
       <c r="C201" s="1" t="inlineStr">
@@ -6837,7 +6845,7 @@
       </c>
       <c r="D201" s="1" t="inlineStr">
         <is>
-          <t>表弟</t>
+          <t>表姐；表妹</t>
         </is>
       </c>
       <c r="E201" s="1" t="inlineStr">
@@ -7115,7 +7123,7 @@
       </c>
       <c r="B210" s="1" t="inlineStr">
         <is>
-          <t>[peʁ.soˈna.ʒẽj̃] 性格&lt;名&gt;</t>
+          <t>[peʁ.soˈna.ʒẽj̃] 人物；角色&lt;名&gt;</t>
         </is>
       </c>
       <c r="C210" s="1" t="inlineStr">
@@ -7125,7 +7133,7 @@
       </c>
       <c r="D210" s="1" t="inlineStr">
         <is>
-          <t>性格</t>
+          <t>人物；角色</t>
         </is>
       </c>
       <c r="E210" s="1" t="inlineStr">
@@ -7312,7 +7320,7 @@
       </c>
       <c r="C216" s="1" t="inlineStr">
         <is>
-          <t>vow.ˈta.ɾãʊ̃</t>
+          <t>/vow.ˈta.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D216" s="1" t="inlineStr">
@@ -7664,7 +7672,7 @@
       </c>
       <c r="C227" s="1" t="inlineStr">
         <is>
-          <t>ˈʒɔy.ə</t>
+          <t>/ˈʒɔy.ə/</t>
         </is>
       </c>
       <c r="D227" s="1" t="inlineStr">
@@ -7723,7 +7731,7 @@
       </c>
       <c r="B229" s="1" t="inlineStr">
         <is>
-          <t>[ˈẽj̃] 呵呵&lt;叹&gt;</t>
+          <t>[ˈẽj̃] 嗯？；啊？&lt;叹&gt;</t>
         </is>
       </c>
       <c r="C229" s="1" t="inlineStr">
@@ -7733,7 +7741,7 @@
       </c>
       <c r="D229" s="1" t="inlineStr">
         <is>
-          <t>呵呵</t>
+          <t>嗯？；啊？</t>
         </is>
       </c>
       <c r="E229" s="1" t="inlineStr">
@@ -7883,7 +7891,7 @@
       </c>
       <c r="B234" s="1" t="inlineStr">
         <is>
-          <t>[ˈblɛ.ki] 黑色&lt;名&gt;</t>
+          <t>[/ˈblɛ.ki/] 黑人（俚语）；黑人的&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C234" s="1" t="inlineStr">
@@ -7893,7 +7901,7 @@
       </c>
       <c r="D234" s="1" t="inlineStr">
         <is>
-          <t>黑色</t>
+          <t>黑人（俚语）；黑人的</t>
         </is>
       </c>
       <c r="E234" s="1" t="inlineStr">
@@ -8939,7 +8947,7 @@
       </c>
       <c r="B267" s="1" t="inlineStr">
         <is>
-          <t>[duˈɾa(ʁ)] 最后&lt;动&gt;</t>
+          <t>[duˈɾa(ʁ)] 持续；持久&lt;动&gt;</t>
         </is>
       </c>
       <c r="C267" s="1" t="inlineStr">
@@ -8949,7 +8957,7 @@
       </c>
       <c r="D267" s="1" t="inlineStr">
         <is>
-          <t>最后</t>
+          <t>持续；持久</t>
         </is>
       </c>
       <c r="E267" s="1" t="inlineStr">
@@ -9008,7 +9016,7 @@
       </c>
       <c r="C269" s="1" t="inlineStr">
         <is>
-          <t>mu.ˈda.ɾãʊ̃</t>
+          <t>/mu.ˈda.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D269" s="1" t="inlineStr">
@@ -9099,7 +9107,7 @@
       </c>
       <c r="B272" s="1" t="inlineStr">
         <is>
-          <t>[ˈfe(j).ɾɐ] 公平&lt;名&gt;</t>
+          <t>[ˈfe(j).ɾɐ] 集市；博览会；交易会&lt;名&gt;</t>
         </is>
       </c>
       <c r="C272" s="1" t="inlineStr">
@@ -9109,7 +9117,7 @@
       </c>
       <c r="D272" s="1" t="inlineStr">
         <is>
-          <t>公平</t>
+          <t>集市；博览会；交易会</t>
         </is>
       </c>
       <c r="E272" s="1" t="inlineStr">
@@ -9264,7 +9272,7 @@
       </c>
       <c r="C277" s="1" t="inlineStr">
         <is>
-          <t>ˈde.ẽỹ</t>
+          <t>/ˈde.ẽỹ/</t>
         </is>
       </c>
       <c r="D277" s="1" t="inlineStr">
@@ -9419,7 +9427,7 @@
       </c>
       <c r="B282" s="1" t="inlineStr">
         <is>
-          <t>[azˈne(j).ɾɐ] 失误&lt;名&gt;</t>
+          <t>[/azˈne(j).ɾɐ/] 蠢话；愚蠢的错误，胡闹&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C282" s="1" t="inlineStr">
@@ -9429,7 +9437,7 @@
       </c>
       <c r="D282" s="1" t="inlineStr">
         <is>
-          <t>失误</t>
+          <t>蠢话；愚蠢的错误，胡闹</t>
         </is>
       </c>
       <c r="E282" s="1" t="inlineStr">
@@ -9582,7 +9590,11 @@
           <t>便士&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C287" s="1" t="inlineStr"/>
+      <c r="C287" s="1" t="inlineStr">
+        <is>
+          <t>/ˈpɛni/</t>
+        </is>
+      </c>
       <c r="D287" s="1" t="inlineStr">
         <is>
           <t>便士</t>
@@ -9735,7 +9747,7 @@
       </c>
       <c r="B292" s="1" t="inlineStr">
         <is>
-          <t>[koˈbɾi(ʁ)] 封面&lt;动&gt;</t>
+          <t>[koˈbɾi(ʁ)] 覆盖；遮盖&lt;动&gt;</t>
         </is>
       </c>
       <c r="C292" s="1" t="inlineStr">
@@ -9745,7 +9757,7 @@
       </c>
       <c r="D292" s="1" t="inlineStr">
         <is>
-          <t>封面</t>
+          <t>覆盖；遮盖</t>
         </is>
       </c>
       <c r="E292" s="1" t="inlineStr">
@@ -10663,7 +10675,7 @@
       </c>
       <c r="B321" s="1" t="inlineStr">
         <is>
-          <t>[ba.zeˈa.du] 联合&lt;名&gt;</t>
+          <t>[ba.zeˈa.du] 基于；以…为基础&lt;名&gt;</t>
         </is>
       </c>
       <c r="C321" s="1" t="inlineStr">
@@ -10673,7 +10685,7 @@
       </c>
       <c r="D321" s="1" t="inlineStr">
         <is>
-          <t>联合</t>
+          <t>基于；以…为基础</t>
         </is>
       </c>
       <c r="E321" s="1" t="inlineStr">
@@ -10700,7 +10712,7 @@
       </c>
       <c r="C322" s="1" t="inlineStr">
         <is>
-          <t>peɣ.ˈde.ɾãʊ̃</t>
+          <t>/peɣ.ˈde.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D322" s="1" t="inlineStr">
@@ -10887,7 +10899,7 @@
       </c>
       <c r="B328" s="1" t="inlineStr">
         <is>
-          <t>[ˈt͡ʃĩ.nɐ] 蒂娜&lt;名&gt;</t>
+          <t>[ˈt͡ʃĩ.nɐ] 大盆；大桶&lt;名&gt;</t>
         </is>
       </c>
       <c r="C328" s="1" t="inlineStr">
@@ -10897,7 +10909,7 @@
       </c>
       <c r="D328" s="1" t="inlineStr">
         <is>
-          <t>蒂娜</t>
+          <t>大盆；大桶</t>
         </is>
       </c>
       <c r="E328" s="1" t="inlineStr">
@@ -11143,7 +11155,7 @@
       </c>
       <c r="B336" s="1" t="inlineStr">
         <is>
-          <t>[ˈũ.ɲɐ] 钉子&lt;名&gt;</t>
+          <t>[ˈũ.ɲɐ] 指甲；趾甲&lt;名&gt;</t>
         </is>
       </c>
       <c r="C336" s="1" t="inlineStr">
@@ -11153,7 +11165,7 @@
       </c>
       <c r="D336" s="1" t="inlineStr">
         <is>
-          <t>钉子</t>
+          <t>指甲；趾甲</t>
         </is>
       </c>
       <c r="E336" s="1" t="inlineStr">
@@ -11532,7 +11544,7 @@
       </c>
       <c r="C348" s="1" t="inlineStr">
         <is>
-          <t>a.tɾa.ˈza.dʊs</t>
+          <t>/a.tɾa.ˈza.dʊs/</t>
         </is>
       </c>
       <c r="D348" s="1" t="inlineStr">
@@ -11788,7 +11800,7 @@
       </c>
       <c r="C356" s="1" t="inlineStr">
         <is>
-          <t>ẽ.ˈtɾa.ɾãʊ̃</t>
+          <t>/ẽ.ˈtɾa.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D356" s="1" t="inlineStr">
@@ -12071,7 +12083,7 @@
       </c>
       <c r="B365" s="1" t="inlineStr">
         <is>
-          <t>[ˈfo.ʎɐ] 片材&lt;名&gt;</t>
+          <t>[/ˈfo.ʎɐ/] 叶子；纸张&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C365" s="1" t="inlineStr">
@@ -12081,7 +12093,7 @@
       </c>
       <c r="D365" s="1" t="inlineStr">
         <is>
-          <t>片材</t>
+          <t>叶子；纸张&lt;名&gt;</t>
         </is>
       </c>
       <c r="E365" s="1" t="inlineStr">
@@ -12903,7 +12915,7 @@
       </c>
       <c r="B391" s="1" t="inlineStr">
         <is>
-          <t>[ˈpo.su] 嗯&lt;名&gt;</t>
+          <t>[ˈpo.su] 井；坑&lt;名&gt;</t>
         </is>
       </c>
       <c r="C391" s="1" t="inlineStr">
@@ -12913,7 +12925,7 @@
       </c>
       <c r="D391" s="1" t="inlineStr">
         <is>
-          <t>嗯</t>
+          <t>井；坑</t>
         </is>
       </c>
       <c r="E391" s="1" t="inlineStr">
@@ -13639,7 +13651,7 @@
       </c>
       <c r="B414" s="1" t="inlineStr">
         <is>
-          <t>[pɾesˈta(ʁ)] 渲染&lt;动&gt;</t>
+          <t>[pɾesˈta(ʁ)] 借出；提供；给予&lt;动&gt;</t>
         </is>
       </c>
       <c r="C414" s="1" t="inlineStr">
@@ -13649,7 +13661,7 @@
       </c>
       <c r="D414" s="1" t="inlineStr">
         <is>
-          <t>渲染</t>
+          <t>借出；提供；给予</t>
         </is>
       </c>
       <c r="E414" s="1" t="inlineStr">
@@ -13740,7 +13752,7 @@
       </c>
       <c r="C417" s="1" t="inlineStr">
         <is>
-          <t>xe.ve.ˈɾẽ.dʊ</t>
+          <t>/xe.ve.ˈɾẽ.dʊ/</t>
         </is>
       </c>
       <c r="D417" s="1" t="inlineStr">
@@ -13836,7 +13848,7 @@
       </c>
       <c r="C420" s="1" t="inlineStr">
         <is>
-          <t>a.tʃi.vi.ˈda.dʒɪ</t>
+          <t>/a.tʃi.vi.ˈda.dʒɪ/</t>
         </is>
       </c>
       <c r="D420" s="1" t="inlineStr">
@@ -14124,7 +14136,7 @@
       </c>
       <c r="C429" s="1" t="inlineStr">
         <is>
-          <t>a.ˈtox</t>
+          <t>/a.ˈtox/</t>
         </is>
       </c>
       <c r="D429" s="1" t="inlineStr">
@@ -14378,7 +14390,11 @@
           <t>玛雅人&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C437" s="1" t="inlineStr"/>
+      <c r="C437" s="1" t="inlineStr">
+        <is>
+          <t>/ˈmaj.a/</t>
+        </is>
+      </c>
       <c r="D437" s="1" t="inlineStr">
         <is>
           <t>玛雅人</t>
@@ -14755,7 +14771,7 @@
       </c>
       <c r="B449" s="1" t="inlineStr">
         <is>
-          <t>[ˈkõ.d͡ʒi] 计数&lt;名&gt;</t>
+          <t>[ˈkõ.d͡ʒi] 伯爵&lt;名&gt;</t>
         </is>
       </c>
       <c r="C449" s="1" t="inlineStr">
@@ -14765,7 +14781,7 @@
       </c>
       <c r="D449" s="1" t="inlineStr">
         <is>
-          <t>计数</t>
+          <t>伯爵</t>
         </is>
       </c>
       <c r="E449" s="1" t="inlineStr">
@@ -14950,7 +14966,11 @@
           <t>荣耀&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C455" s="1" t="inlineStr"/>
+      <c r="C455" s="1" t="inlineStr">
+        <is>
+          <t>/ˈɡlɔ.ɾjɐ/</t>
+        </is>
+      </c>
       <c r="D455" s="1" t="inlineStr">
         <is>
           <t>荣耀</t>
@@ -15263,7 +15283,7 @@
       </c>
       <c r="B465" s="1" t="inlineStr">
         <is>
-          <t>[na.moˈɾa(ʁ)] 日期&lt;动&gt;</t>
+          <t>[na.moˈɾa(ʁ)] 恋爱；约会&lt;动&gt;</t>
         </is>
       </c>
       <c r="C465" s="1" t="inlineStr">
@@ -15273,7 +15293,7 @@
       </c>
       <c r="D465" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>恋爱；约会</t>
         </is>
       </c>
       <c r="E465" s="1" t="inlineStr">
@@ -15295,7 +15315,7 @@
       </c>
       <c r="B466" s="1" t="inlineStr">
         <is>
-          <t>[ˈbe.bu] 喝&lt;名&gt;</t>
+          <t>[/ˈbe.bu/] 喝（eu bebo，动词beber的第一人称单数现在式）&lt;动&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C466" s="1" t="inlineStr">
@@ -15305,7 +15325,7 @@
       </c>
       <c r="D466" s="1" t="inlineStr">
         <is>
-          <t>喝</t>
+          <t>喝（eu bebo，动词beber的第一人称单数现在式）&lt;动&gt;</t>
         </is>
       </c>
       <c r="E466" s="1" t="inlineStr">
@@ -16356,7 +16376,7 @@
       </c>
       <c r="C499" s="1" t="inlineStr">
         <is>
-          <t>ˈsĩ.zəs</t>
+          <t>/ˈsĩ.zəs/</t>
         </is>
       </c>
       <c r="D499" s="1" t="inlineStr">
@@ -16735,7 +16755,7 @@
       </c>
       <c r="B511" s="1" t="inlineStr">
         <is>
-          <t>[ˈmɐ̃.du] 我发送&lt;名&gt;</t>
+          <t>[ˈmɐ̃.du] 命令；指挥；控制；方向盘&lt;名&gt;</t>
         </is>
       </c>
       <c r="C511" s="1" t="inlineStr">
@@ -16745,7 +16765,7 @@
       </c>
       <c r="D511" s="1" t="inlineStr">
         <is>
-          <t>我发送</t>
+          <t>命令；指挥；控制；方向盘</t>
         </is>
       </c>
       <c r="E511" s="1" t="inlineStr">
@@ -17311,7 +17331,7 @@
       </c>
       <c r="B529" s="1" t="inlineStr">
         <is>
-          <t>[ʁeˈmɛ.d͡ʒju] 医学&lt;名&gt;</t>
+          <t>[ʁeˈmɛ.d͡ʒju] 药；药物&lt;名&gt;</t>
         </is>
       </c>
       <c r="C529" s="1" t="inlineStr">
@@ -17321,7 +17341,7 @@
       </c>
       <c r="D529" s="1" t="inlineStr">
         <is>
-          <t>医学</t>
+          <t>药；药物</t>
         </is>
       </c>
       <c r="E529" s="1" t="inlineStr">
@@ -17375,7 +17395,7 @@
       </c>
       <c r="B531" s="1" t="inlineStr">
         <is>
-          <t>[is.kwaˈdɾɐ̃w̃] 小队&lt;名&gt;</t>
+          <t>[/is.kwaˈdɾɐ̃w̃/] 中队；飞行队；警察特别行动队&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C531" s="1" t="inlineStr">
@@ -17385,7 +17405,7 @@
       </c>
       <c r="D531" s="1" t="inlineStr">
         <is>
-          <t>小队</t>
+          <t>中队；飞行队；警察特别行动队&lt;名&gt;</t>
         </is>
       </c>
       <c r="E531" s="1" t="inlineStr">
@@ -17476,7 +17496,7 @@
       </c>
       <c r="C534" s="1" t="inlineStr">
         <is>
-          <t>des.ko.ˈbɾi.ɾãʊ̃</t>
+          <t>/des.ko.ˈbɾi.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D534" s="1" t="inlineStr">
@@ -17567,7 +17587,7 @@
       </c>
       <c r="B537" s="1" t="inlineStr">
         <is>
-          <t>[kɐ̃.pi.oˈna.tu] 冠军&lt;名&gt;</t>
+          <t>[kɐ̃.pi.oˈna.tu] 锦标赛；联赛&lt;名&gt;</t>
         </is>
       </c>
       <c r="C537" s="1" t="inlineStr">
@@ -17577,7 +17597,7 @@
       </c>
       <c r="D537" s="1" t="inlineStr">
         <is>
-          <t>冠军</t>
+          <t>锦标赛；联赛</t>
         </is>
       </c>
       <c r="E537" s="1" t="inlineStr">
@@ -17887,7 +17907,7 @@
       </c>
       <c r="B547" s="1" t="inlineStr">
         <is>
-          <t>[ˈkɾi.ɐ] 创造&lt;名&gt;</t>
+          <t>[ˈkɾi.ɐ] 创造；幼崽&lt;名&gt;</t>
         </is>
       </c>
       <c r="C547" s="1" t="inlineStr">
@@ -17897,7 +17917,7 @@
       </c>
       <c r="D547" s="1" t="inlineStr">
         <is>
-          <t>创造</t>
+          <t>创造；幼崽</t>
         </is>
       </c>
       <c r="E547" s="1" t="inlineStr">
@@ -17924,7 +17944,7 @@
       </c>
       <c r="C548" s="1" t="inlineStr">
         <is>
-          <t>vi.to.ˈɾi.ə</t>
+          <t>/vi.to.ˈɾi.ə/</t>
         </is>
       </c>
       <c r="D548" s="1" t="inlineStr">
@@ -17988,7 +18008,7 @@
       </c>
       <c r="C550" s="1" t="inlineStr">
         <is>
-          <t>ak.tu.ˈaw</t>
+          <t>/ak.tu.ˈaw/</t>
         </is>
       </c>
       <c r="D550" s="1" t="inlineStr">
@@ -18207,7 +18227,7 @@
       </c>
       <c r="B557" s="1" t="inlineStr">
         <is>
-          <t>[e.vẽ.tuˌawˈmẽ.t͡ʃi] 最终&lt;副&gt;</t>
+          <t>[e.vẽ.tuˌawˈmẽ.t͡ʃi] 可能；偶尔；碰巧&lt;副&gt;</t>
         </is>
       </c>
       <c r="C557" s="1" t="inlineStr">
@@ -18217,7 +18237,7 @@
       </c>
       <c r="D557" s="1" t="inlineStr">
         <is>
-          <t>最终</t>
+          <t>可能；偶尔；碰巧</t>
         </is>
       </c>
       <c r="E557" s="1" t="inlineStr">
@@ -18431,7 +18451,7 @@
       </c>
       <c r="B564" s="1" t="inlineStr">
         <is>
-          <t>[de.ʁoˈta(ʁ)] 失败&lt;动&gt;</t>
+          <t>[de.ʁoˈta(ʁ)] 打败；击败&lt;动&gt;</t>
         </is>
       </c>
       <c r="C564" s="1" t="inlineStr">
@@ -18441,7 +18461,7 @@
       </c>
       <c r="D564" s="1" t="inlineStr">
         <is>
-          <t>失败</t>
+          <t>打败；击败</t>
         </is>
       </c>
       <c r="E564" s="1" t="inlineStr">
@@ -18463,7 +18483,7 @@
       </c>
       <c r="B565" s="1" t="inlineStr">
         <is>
-          <t>[des.peʁ.d͡ʒiˈsa(ʁ)] 废物&lt;动&gt;</t>
+          <t>[des.peʁ.d͡ʒiˈsa(ʁ)] 浪费&lt;动&gt;</t>
         </is>
       </c>
       <c r="C565" s="1" t="inlineStr">
@@ -18473,7 +18493,7 @@
       </c>
       <c r="D565" s="1" t="inlineStr">
         <is>
-          <t>废物</t>
+          <t>浪费</t>
         </is>
       </c>
       <c r="E565" s="1" t="inlineStr">
@@ -18591,7 +18611,7 @@
       </c>
       <c r="B569" s="1" t="inlineStr">
         <is>
-          <t>[ʁeˈve(ʁ)] 评论&lt;动&gt;</t>
+          <t>[ʁeˈve(ʁ)] 重看；复查；修订&lt;动&gt;</t>
         </is>
       </c>
       <c r="C569" s="1" t="inlineStr">
@@ -18601,7 +18621,7 @@
       </c>
       <c r="D569" s="1" t="inlineStr">
         <is>
-          <t>评论</t>
+          <t>重看；复查；修订</t>
         </is>
       </c>
       <c r="E569" s="1" t="inlineStr">
@@ -19332,7 +19352,7 @@
       </c>
       <c r="C592" s="1" t="inlineStr">
         <is>
-          <t>a dʒi</t>
+          <t>/a dʒi/</t>
         </is>
       </c>
       <c r="D592" s="1" t="inlineStr">
@@ -20223,7 +20243,7 @@
       </c>
       <c r="B620" s="1" t="inlineStr">
         <is>
-          <t>[ˈmaj.u] 可能&lt;名&gt;</t>
+          <t>[ˈmaj.u] 五月&lt;名&gt;</t>
         </is>
       </c>
       <c r="C620" s="1" t="inlineStr">
@@ -20233,7 +20253,7 @@
       </c>
       <c r="D620" s="1" t="inlineStr">
         <is>
-          <t>可能</t>
+          <t>五月</t>
         </is>
       </c>
       <c r="E620" s="1" t="inlineStr">
@@ -20511,7 +20531,7 @@
       </c>
       <c r="B629" s="1" t="inlineStr">
         <is>
-          <t>[d͡ʒis.po.ziˈsɐ̃w̃] 性格&lt;名&gt;</t>
+          <t>[/d͡ʒis.po.ziˈsɐ̃w̃/] 安排；处置；性情&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C629" s="1" t="inlineStr">
@@ -20521,7 +20541,7 @@
       </c>
       <c r="D629" s="1" t="inlineStr">
         <is>
-          <t>性格</t>
+          <t>安排；处置；性情&lt;名&gt;</t>
         </is>
       </c>
       <c r="E629" s="1" t="inlineStr">
@@ -20639,7 +20659,7 @@
       </c>
       <c r="B633" s="1" t="inlineStr">
         <is>
-          <t>[a.pɾo.siˈma(ʁ)] 方法&lt;动&gt;</t>
+          <t>[a.pɾo.siˈma(ʁ)] 使靠近；接近&lt;动&gt;</t>
         </is>
       </c>
       <c r="C633" s="1" t="inlineStr">
@@ -20649,7 +20669,7 @@
       </c>
       <c r="D633" s="1" t="inlineStr">
         <is>
-          <t>方法</t>
+          <t>使靠近；接近</t>
         </is>
       </c>
       <c r="E633" s="1" t="inlineStr">
@@ -21124,7 +21144,7 @@
       </c>
       <c r="C648" s="1" t="inlineStr">
         <is>
-          <t>ko.le.ˈsãʊ̃</t>
+          <t>/ko.le.ˈsãʊ̃/</t>
         </is>
       </c>
       <c r="D648" s="1" t="inlineStr">
@@ -21151,7 +21171,7 @@
       </c>
       <c r="B649" s="1" t="inlineStr">
         <is>
-          <t>[ˈlew] 读&lt;名&gt;</t>
+          <t>[ˈlew] 读了&lt;名&gt;</t>
         </is>
       </c>
       <c r="C649" s="1" t="inlineStr">
@@ -21161,7 +21181,7 @@
       </c>
       <c r="D649" s="1" t="inlineStr">
         <is>
-          <t>读</t>
+          <t>读了</t>
         </is>
       </c>
       <c r="E649" s="1" t="inlineStr">
@@ -21476,7 +21496,7 @@
       </c>
       <c r="C659" s="1" t="inlineStr">
         <is>
-          <t>a.pã.ˈɲa.ɾãʊ̃</t>
+          <t>/a.pã.ˈɲa.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D659" s="1" t="inlineStr">
@@ -21956,7 +21976,7 @@
       </c>
       <c r="C674" s="1" t="inlineStr">
         <is>
-          <t>ob.ˈʒɛ.tʊ</t>
+          <t>/ob.ˈʒɛ.tʊ/</t>
         </is>
       </c>
       <c r="D674" s="1" t="inlineStr">
@@ -22111,7 +22131,7 @@
       </c>
       <c r="B679" s="1" t="inlineStr">
         <is>
-          <t>[a.teˈʁa(ʁ)] 土地&lt;动&gt;</t>
+          <t>[a.teˈʁa(ʁ)] 着陆；降落&lt;动&gt;</t>
         </is>
       </c>
       <c r="C679" s="1" t="inlineStr">
@@ -22121,7 +22141,7 @@
       </c>
       <c r="D679" s="1" t="inlineStr">
         <is>
-          <t>土地</t>
+          <t>着陆；降落</t>
         </is>
       </c>
       <c r="E679" s="1" t="inlineStr">
@@ -22175,7 +22195,7 @@
       </c>
       <c r="B681" s="1" t="inlineStr">
         <is>
-          <t>[floˈɾi.du] 华丽的&lt;形&gt;</t>
+          <t>[/floˈɾi.du/] 盛开的&lt;形&gt;；花繁茂的&lt;形&gt;&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C681" s="1" t="inlineStr">
@@ -22185,7 +22205,7 @@
       </c>
       <c r="D681" s="1" t="inlineStr">
         <is>
-          <t>华丽的</t>
+          <t>盛开的&lt;形&gt;；花繁茂的&lt;形&gt;</t>
         </is>
       </c>
       <c r="E681" s="1" t="inlineStr">
@@ -22239,7 +22259,7 @@
       </c>
       <c r="B683" s="1" t="inlineStr">
         <is>
-          <t>[ˈʁɔ.ʃɐ] 摇滚&lt;名&gt;</t>
+          <t>[ˈʁɔ.ʃɐ] 岩石&lt;名&gt;</t>
         </is>
       </c>
       <c r="C683" s="1" t="inlineStr">
@@ -22249,7 +22269,7 @@
       </c>
       <c r="D683" s="1" t="inlineStr">
         <is>
-          <t>摇滚</t>
+          <t>岩石</t>
         </is>
       </c>
       <c r="E683" s="1" t="inlineStr">
@@ -22500,7 +22520,7 @@
       </c>
       <c r="C691" s="1" t="inlineStr">
         <is>
-          <t>bo</t>
+          <t>/bo/</t>
         </is>
       </c>
       <c r="D691" s="1" t="inlineStr">
@@ -22591,7 +22611,7 @@
       </c>
       <c r="B694" s="1" t="inlineStr">
         <is>
-          <t>[pɾo.seˈsa(ʁ)] 过程&lt;动&gt;</t>
+          <t>[pɾo.seˈsa(ʁ)] 处理；加工；起诉&lt;动&gt;</t>
         </is>
       </c>
       <c r="C694" s="1" t="inlineStr">
@@ -22601,7 +22621,7 @@
       </c>
       <c r="D694" s="1" t="inlineStr">
         <is>
-          <t>过程</t>
+          <t>处理；加工；起诉</t>
         </is>
       </c>
       <c r="E694" s="1" t="inlineStr">
@@ -22655,7 +22675,7 @@
       </c>
       <c r="B696" s="1" t="inlineStr">
         <is>
-          <t>[a.mɐ̃.ɲeˈseʁ] 黎明&lt;名&gt;</t>
+          <t>[/a.mɐ̃.ɲeˈseʁ/] 破晓&lt;动&gt;；天亮&lt;动&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C696" s="1" t="inlineStr">
@@ -22665,7 +22685,7 @@
       </c>
       <c r="D696" s="1" t="inlineStr">
         <is>
-          <t>黎明</t>
+          <t>破晓&lt;动&gt;；天亮&lt;动&gt;</t>
         </is>
       </c>
       <c r="E696" s="1" t="inlineStr">
@@ -22815,7 +22835,7 @@
       </c>
       <c r="B701" s="1" t="inlineStr">
         <is>
-          <t>[ˈpla.kɐ] 董事会&lt;名&gt;</t>
+          <t>[ˈpla.kɐ] 板；牌；匾&lt;名&gt;</t>
         </is>
       </c>
       <c r="C701" s="1" t="inlineStr">
@@ -22825,7 +22845,7 @@
       </c>
       <c r="D701" s="1" t="inlineStr">
         <is>
-          <t>董事会</t>
+          <t>板；牌；匾</t>
         </is>
       </c>
       <c r="E701" s="1" t="inlineStr">
@@ -22847,13 +22867,17 @@
       </c>
       <c r="B702" s="1" t="inlineStr">
         <is>
-          <t>戴尔&lt;叹&gt;</t>
-        </is>
-      </c>
-      <c r="C702" s="1" t="inlineStr"/>
+          <t>加油；上啊&lt;叹&gt;</t>
+        </is>
+      </c>
+      <c r="C702" s="1" t="inlineStr">
+        <is>
+          <t>/ˈda.li/</t>
+        </is>
+      </c>
       <c r="D702" s="1" t="inlineStr">
         <is>
-          <t>戴尔</t>
+          <t>加油；上啊</t>
         </is>
       </c>
       <c r="E702" s="1" t="inlineStr">
@@ -23067,7 +23091,7 @@
       </c>
       <c r="B709" s="1" t="inlineStr">
         <is>
-          <t>[pi.eˈda.d͡ʒi] 虔诚&lt;名&gt;</t>
+          <t>[/pi.eˈda.d͡ʒi/] 怜悯；慈悲&lt;名&gt;（亦有“虔诚”义）&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C709" s="1" t="inlineStr">
@@ -23077,7 +23101,7 @@
       </c>
       <c r="D709" s="1" t="inlineStr">
         <is>
-          <t>虔诚</t>
+          <t>怜悯；慈悲&lt;名&gt;（亦有“虔诚”义）</t>
         </is>
       </c>
       <c r="E709" s="1" t="inlineStr">
@@ -23707,7 +23731,7 @@
       </c>
       <c r="B729" s="1" t="inlineStr">
         <is>
-          <t>[pesˈka(ʁ)] 鱼&lt;动&gt;</t>
+          <t>[pesˈka(ʁ)] 钓鱼；捕鱼&lt;动&gt;</t>
         </is>
       </c>
       <c r="C729" s="1" t="inlineStr">
@@ -23717,7 +23741,7 @@
       </c>
       <c r="D729" s="1" t="inlineStr">
         <is>
-          <t>鱼</t>
+          <t>钓鱼；捕鱼</t>
         </is>
       </c>
       <c r="E729" s="1" t="inlineStr">
@@ -24315,7 +24339,7 @@
       </c>
       <c r="B748" s="1" t="inlineStr">
         <is>
-          <t>[a.keˈse(ʁ)] 热身&lt;动&gt;</t>
+          <t>[/a.keˈse(ʁ)/] 加热；使变热&lt;动&gt;&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C748" s="1" t="inlineStr">
@@ -24325,7 +24349,7 @@
       </c>
       <c r="D748" s="1" t="inlineStr">
         <is>
-          <t>热身</t>
+          <t>加热；使变热&lt;动&gt;</t>
         </is>
       </c>
       <c r="E748" s="1" t="inlineStr">
@@ -24830,7 +24854,11 @@
           <t>已经&lt;副&gt;</t>
         </is>
       </c>
-      <c r="C764" s="1" t="inlineStr"/>
+      <c r="C764" s="1" t="inlineStr">
+        <is>
+          <t>/ʒa/</t>
+        </is>
+      </c>
       <c r="D764" s="1" t="inlineStr">
         <is>
           <t>已经</t>
@@ -24956,7 +24984,7 @@
       </c>
       <c r="C768" s="1" t="inlineStr">
         <is>
-          <t>istaʁ</t>
+          <t>/istaʁ/</t>
         </is>
       </c>
       <c r="D768" s="1" t="inlineStr">
@@ -25079,7 +25107,7 @@
       </c>
       <c r="B772" s="1" t="inlineStr">
         <is>
-          <t>[ĩ.d͡ʒiˈvi.d(w)u] 个人的&lt;名&gt;</t>
+          <t>[ĩ.d͡ʒiˈvi.d(w)u] 个人；个体&lt;名&gt;</t>
         </is>
       </c>
       <c r="C772" s="1" t="inlineStr">
@@ -25089,7 +25117,7 @@
       </c>
       <c r="D772" s="1" t="inlineStr">
         <is>
-          <t>个人的</t>
+          <t>个人；个体</t>
         </is>
       </c>
       <c r="E772" s="1" t="inlineStr">
@@ -25143,7 +25171,7 @@
       </c>
       <c r="B774" s="1" t="inlineStr">
         <is>
-          <t>[ˈtɾo.ku] 改变&lt;名&gt;</t>
+          <t>[ˈtɾo.ku] 找零；找头&lt;名&gt;</t>
         </is>
       </c>
       <c r="C774" s="1" t="inlineStr">
@@ -25153,7 +25181,7 @@
       </c>
       <c r="D774" s="1" t="inlineStr">
         <is>
-          <t>改变</t>
+          <t>找零；找头</t>
         </is>
       </c>
       <c r="E774" s="1" t="inlineStr">
@@ -25692,7 +25720,7 @@
       </c>
       <c r="C791" s="1" t="inlineStr">
         <is>
-          <t>e.le.tɾi.si.ˈda.dʒɪ</t>
+          <t>/e.le.tɾi.si.ˈda.dʒɪ/</t>
         </is>
       </c>
       <c r="D791" s="1" t="inlineStr">
@@ -25911,7 +25939,7 @@
       </c>
       <c r="B798" s="1" t="inlineStr">
         <is>
-          <t>[a.ɡɾaˈda(ʁ)] 请&lt;动&gt;</t>
+          <t>[a.ɡɾaˈda(ʁ)] 取悦；使高兴；使满意&lt;动&gt;</t>
         </is>
       </c>
       <c r="C798" s="1" t="inlineStr">
@@ -25921,7 +25949,7 @@
       </c>
       <c r="D798" s="1" t="inlineStr">
         <is>
-          <t>请</t>
+          <t>取悦；使高兴；使满意</t>
         </is>
       </c>
       <c r="E798" s="1" t="inlineStr">
@@ -25980,7 +26008,7 @@
       </c>
       <c r="C800" s="1" t="inlineStr">
         <is>
-          <t>xow.ˈba.ɾãʊ̃</t>
+          <t>/xow.ˈba.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D800" s="1" t="inlineStr">
@@ -26076,7 +26104,7 @@
       </c>
       <c r="C803" s="1" t="inlineStr">
         <is>
-          <t>dɔˈtɔɾ</t>
+          <t>/dɔˈtɔɾ/</t>
         </is>
       </c>
       <c r="D803" s="1" t="inlineStr">
@@ -26615,17 +26643,17 @@
       </c>
       <c r="B820" s="1" t="inlineStr">
         <is>
-          <t>[sɔ] 所以&lt;名&gt;</t>
+          <t>[sɔ] só：只；仅仅&lt;副&gt;（应带重音符号 só）&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C820" s="1" t="inlineStr">
         <is>
-          <t>sɔ</t>
+          <t>/sɔ/</t>
         </is>
       </c>
       <c r="D820" s="1" t="inlineStr">
         <is>
-          <t>所以</t>
+          <t>só：只；仅仅&lt;副&gt;（应带重音符号 só）</t>
         </is>
       </c>
       <c r="E820" s="1" t="inlineStr">
@@ -26711,7 +26739,7 @@
       </c>
       <c r="B823" s="1" t="inlineStr">
         <is>
-          <t>[sĩˈkwẽ.tɐ] 五十&lt;名&gt;</t>
+          <t>[/sĩˈkwẽ.tɐ/] 五十&lt;数&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C823" s="1" t="inlineStr">
@@ -26721,7 +26749,7 @@
       </c>
       <c r="D823" s="1" t="inlineStr">
         <is>
-          <t>五十</t>
+          <t>五十&lt;数&gt;</t>
         </is>
       </c>
       <c r="E823" s="1" t="inlineStr">
@@ -26871,7 +26899,7 @@
       </c>
       <c r="B828" s="1" t="inlineStr">
         <is>
-          <t>[a.ʁu.iˈna(ʁ)] 废墟&lt;动&gt;</t>
+          <t>[a.ʁu.iˈna(ʁ)] 毁坏；破坏；使毁灭&lt;动&gt;</t>
         </is>
       </c>
       <c r="C828" s="1" t="inlineStr">
@@ -26881,7 +26909,7 @@
       </c>
       <c r="D828" s="1" t="inlineStr">
         <is>
-          <t>废墟</t>
+          <t>毁坏；破坏；使毁灭</t>
         </is>
       </c>
       <c r="E828" s="1" t="inlineStr">
@@ -27415,7 +27443,7 @@
       </c>
       <c r="B845" s="1" t="inlineStr">
         <is>
-          <t>[ˈvɛs.t͡ʃi] 磨损&lt;名&gt;</t>
+          <t>[ˈvɛs.t͡ʃi] 服装；衣服&lt;名&gt;</t>
         </is>
       </c>
       <c r="C845" s="1" t="inlineStr">
@@ -27425,7 +27453,7 @@
       </c>
       <c r="D845" s="1" t="inlineStr">
         <is>
-          <t>磨损</t>
+          <t>服装；衣服</t>
         </is>
       </c>
       <c r="E845" s="1" t="inlineStr">
@@ -27799,7 +27827,7 @@
       </c>
       <c r="B857" s="1" t="inlineStr">
         <is>
-          <t>[ɡaˈlak.sjɐ] 银河系&lt;名&gt;</t>
+          <t>[/ɡaˈlak.sjɐ/] 星系；银河&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C857" s="1" t="inlineStr">
@@ -27809,7 +27837,7 @@
       </c>
       <c r="D857" s="1" t="inlineStr">
         <is>
-          <t>银河系</t>
+          <t>星系；银河&lt;名&gt;</t>
         </is>
       </c>
       <c r="E857" s="1" t="inlineStr">
@@ -27930,7 +27958,11 @@
           <t>牛仔&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C861" s="1" t="inlineStr"/>
+      <c r="C861" s="1" t="inlineStr">
+        <is>
+          <t>/ˈkaʊ.bɔɪ/</t>
+        </is>
+      </c>
       <c r="D861" s="1" t="inlineStr">
         <is>
           <t>牛仔</t>
@@ -28979,7 +29011,7 @@
       </c>
       <c r="B894" s="1" t="inlineStr">
         <is>
-          <t>[foʁˈma(ʁ)] 形式&lt;动&gt;</t>
+          <t>[foʁˈma(ʁ)] 形成；组成；培养&lt;动&gt;</t>
         </is>
       </c>
       <c r="C894" s="1" t="inlineStr">
@@ -28989,7 +29021,7 @@
       </c>
       <c r="D894" s="1" t="inlineStr">
         <is>
-          <t>形式</t>
+          <t>形成；组成；培养</t>
         </is>
       </c>
       <c r="E894" s="1" t="inlineStr">
@@ -29048,7 +29080,7 @@
       </c>
       <c r="C896" s="1" t="inlineStr">
         <is>
-          <t>ˈtɛ.tʊ</t>
+          <t>/ˈtɛ.tʊ/</t>
         </is>
       </c>
       <c r="D896" s="1" t="inlineStr">
@@ -29139,7 +29171,7 @@
       </c>
       <c r="B899" s="1" t="inlineStr">
         <is>
-          <t>[a.piˈli.du] 昵称&lt;名&gt;</t>
+          <t>[/a.piˈli.du/] 姓氏（欧葡）；昵称（巴葡）&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C899" s="1" t="inlineStr">
@@ -29149,7 +29181,7 @@
       </c>
       <c r="D899" s="1" t="inlineStr">
         <is>
-          <t>昵称</t>
+          <t>姓氏（欧葡）；昵称（巴葡）</t>
         </is>
       </c>
       <c r="E899" s="1" t="inlineStr">
@@ -29174,7 +29206,11 @@
           <t>昆虫&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C900" s="1" t="inlineStr"/>
+      <c r="C900" s="1" t="inlineStr">
+        <is>
+          <t>/ĩˈsɛk.tu/</t>
+        </is>
+      </c>
       <c r="D900" s="1" t="inlineStr">
         <is>
           <t>昆虫</t>
@@ -29231,7 +29267,7 @@
       </c>
       <c r="B902" s="1" t="inlineStr">
         <is>
-          <t>[ˈfɾɐ̃.ku] 弗兰克&lt;名&gt;</t>
+          <t>[ˈfɾɐ̃.ku] 坦率的；坦白的；法郎&lt;名&gt;</t>
         </is>
       </c>
       <c r="C902" s="1" t="inlineStr">
@@ -29241,7 +29277,7 @@
       </c>
       <c r="D902" s="1" t="inlineStr">
         <is>
-          <t>弗兰克</t>
+          <t>坦率的；坦白的；法郎</t>
         </is>
       </c>
       <c r="E902" s="1" t="inlineStr">
@@ -29362,10 +29398,14 @@
           <t>灰色&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C906" s="1" t="inlineStr"/>
+      <c r="C906" s="1" t="inlineStr">
+        <is>
+          <t>/ɡreɪ/</t>
+        </is>
+      </c>
       <c r="D906" s="1" t="inlineStr">
         <is>
-          <t>灰色</t>
+          <t>非葡萄牙语词条（英语词），应删除或改为 cinza 灰色&lt;名&gt;</t>
         </is>
       </c>
       <c r="E906" s="1" t="inlineStr">
@@ -29646,7 +29686,11 @@
           <t>c.&lt;副&gt;</t>
         </is>
       </c>
-      <c r="C915" s="1" t="inlineStr"/>
+      <c r="C915" s="1" t="inlineStr">
+        <is>
+          <t>/se/</t>
+        </is>
+      </c>
       <c r="D915" s="1" t="inlineStr">
         <is>
           <t>c.</t>
@@ -30599,7 +30643,7 @@
       </c>
       <c r="B945" s="1" t="inlineStr">
         <is>
-          <t>[leˈvɐ̃.t͡ʃi] 电梯&lt;名&gt;</t>
+          <t>[leˈvɐ̃.t͡ʃi] 起义；暴动；升起&lt;名&gt;</t>
         </is>
       </c>
       <c r="C945" s="1" t="inlineStr">
@@ -30609,7 +30653,7 @@
       </c>
       <c r="D945" s="1" t="inlineStr">
         <is>
-          <t>电梯</t>
+          <t>起义；暴动；升起</t>
         </is>
       </c>
       <c r="E945" s="1" t="inlineStr">
@@ -31015,7 +31059,7 @@
       </c>
       <c r="B958" s="1" t="inlineStr">
         <is>
-          <t>[ko.ʁiˈʒi(ʁ)] 正确&lt;动&gt;</t>
+          <t>[ko.ʁiˈʒi(ʁ)] 改正；纠正；批改&lt;动&gt;</t>
         </is>
       </c>
       <c r="C958" s="1" t="inlineStr">
@@ -31025,7 +31069,7 @@
       </c>
       <c r="D958" s="1" t="inlineStr">
         <is>
-          <t>正确</t>
+          <t>改正；纠正；批改</t>
         </is>
       </c>
       <c r="E958" s="1" t="inlineStr">
@@ -31047,7 +31091,7 @@
       </c>
       <c r="B959" s="1" t="inlineStr">
         <is>
-          <t>[ˈdu.ki] 杜克大学&lt;名&gt;</t>
+          <t>[ˈdu.ki] 公爵&lt;名&gt;</t>
         </is>
       </c>
       <c r="C959" s="1" t="inlineStr">
@@ -31057,7 +31101,7 @@
       </c>
       <c r="D959" s="1" t="inlineStr">
         <is>
-          <t>杜克大学</t>
+          <t>公爵</t>
         </is>
       </c>
       <c r="E959" s="1" t="inlineStr">
@@ -31274,7 +31318,11 @@
           <t>可汗&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C966" s="1" t="inlineStr"/>
+      <c r="C966" s="1" t="inlineStr">
+        <is>
+          <t>/kɑːn/</t>
+        </is>
+      </c>
       <c r="D966" s="1" t="inlineStr">
         <is>
           <t>可汗</t>
@@ -31299,7 +31347,7 @@
       </c>
       <c r="B967" s="1" t="inlineStr">
         <is>
-          <t>[ˈmɛ.djɐ] 媒体&lt;名&gt;</t>
+          <t>[/ˈmɛ.djɐ/] 平均数&lt;名&gt;；媒体&lt;名&gt;（应为média）&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C967" s="1" t="inlineStr">
@@ -31309,7 +31357,7 @@
       </c>
       <c r="D967" s="1" t="inlineStr">
         <is>
-          <t>媒体</t>
+          <t>平均数&lt;名&gt;；媒体&lt;名&gt;（应为média）</t>
         </is>
       </c>
       <c r="E967" s="1" t="inlineStr">
@@ -31875,7 +31923,7 @@
       </c>
       <c r="B985" s="1" t="inlineStr">
         <is>
-          <t>[ˈtɾa.fi.ku] 交通&lt;名&gt;</t>
+          <t>[ˈtɾa.fi.ku] 非法贩运；走私&lt;名&gt;</t>
         </is>
       </c>
       <c r="C985" s="1" t="inlineStr">
@@ -31885,7 +31933,7 @@
       </c>
       <c r="D985" s="1" t="inlineStr">
         <is>
-          <t>交通</t>
+          <t>非法贩运；走私</t>
         </is>
       </c>
       <c r="E985" s="1" t="inlineStr">
@@ -32166,7 +32214,11 @@
           <t>嗯&lt;叹&gt;</t>
         </is>
       </c>
-      <c r="C994" s="1" t="inlineStr"/>
+      <c r="C994" s="1" t="inlineStr">
+        <is>
+          <t>/mm/</t>
+        </is>
+      </c>
       <c r="D994" s="1" t="inlineStr">
         <is>
           <t>嗯</t>
@@ -32772,7 +32824,7 @@
       </c>
       <c r="C1013" s="1" t="inlineStr">
         <is>
-          <t>a.ˈtɾis</t>
+          <t>/a.ˈtɾis/</t>
         </is>
       </c>
       <c r="D1013" s="1" t="inlineStr">
@@ -33215,7 +33267,7 @@
       </c>
       <c r="B1027" s="1" t="inlineStr">
         <is>
-          <t>[pẽˈsa.ɾɐ̃w̃] 思想&lt;动&gt;</t>
+          <t>[pẽˈsa.ɾɐ̃w̃] 他们想；他们思考&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1027" s="1" t="inlineStr">
@@ -33225,7 +33277,7 @@
       </c>
       <c r="D1027" s="1" t="inlineStr">
         <is>
-          <t>思想</t>
+          <t>他们想；他们思考</t>
         </is>
       </c>
       <c r="E1027" s="1" t="inlineStr">
@@ -33442,7 +33494,11 @@
           <t>我的&lt;代&gt;</t>
         </is>
       </c>
-      <c r="C1034" s="1" t="inlineStr"/>
+      <c r="C1034" s="1" t="inlineStr">
+        <is>
+          <t>/my/</t>
+        </is>
+      </c>
       <c r="D1034" s="1" t="inlineStr">
         <is>
           <t>我的</t>
@@ -34208,7 +34264,7 @@
       </c>
       <c r="C1058" s="1" t="inlineStr">
         <is>
-          <t>a.pa.ɾe.ˈse.ɾãʊ̃</t>
+          <t>/a.pa.ɾe.ˈse.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D1058" s="1" t="inlineStr">
@@ -34235,7 +34291,7 @@
       </c>
       <c r="B1059" s="1" t="inlineStr">
         <is>
-          <t>[ʁe.moˈve(ʁ)] 删除&lt;动&gt;</t>
+          <t>[/ʁe.moˈve(ʁ)/] 移除，去除&lt;动&gt;&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1059" s="1" t="inlineStr">
@@ -34245,7 +34301,7 @@
       </c>
       <c r="D1059" s="1" t="inlineStr">
         <is>
-          <t>删除</t>
+          <t>移除，去除&lt;动&gt;</t>
         </is>
       </c>
       <c r="E1059" s="1" t="inlineStr">
@@ -34331,7 +34387,7 @@
       </c>
       <c r="B1062" s="1" t="inlineStr">
         <is>
-          <t>[ˈɡo.tɐ] 痛风&lt;名&gt;</t>
+          <t>[/ˈɡo.tɐ/] 水滴，滴&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1062" s="1" t="inlineStr">
@@ -34341,7 +34397,7 @@
       </c>
       <c r="D1062" s="1" t="inlineStr">
         <is>
-          <t>痛风</t>
+          <t>水滴，滴&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1062" s="1" t="inlineStr">
@@ -34363,7 +34419,7 @@
       </c>
       <c r="B1063" s="1" t="inlineStr">
         <is>
-          <t>[li.deˈɾa(ʁ)] 铅&lt;动&gt;</t>
+          <t>[li.deˈɾa(ʁ)] 领导；带领&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1063" s="1" t="inlineStr">
@@ -34373,7 +34429,7 @@
       </c>
       <c r="D1063" s="1" t="inlineStr">
         <is>
-          <t>铅</t>
+          <t>领导；带领</t>
         </is>
       </c>
       <c r="E1063" s="1" t="inlineStr">
@@ -34816,7 +34872,7 @@
       </c>
       <c r="C1077" s="1" t="inlineStr">
         <is>
-          <t>e.sep.ˈsãʊ̃</t>
+          <t>/e.sep.ˈsãʊ̃/</t>
         </is>
       </c>
       <c r="D1077" s="1" t="inlineStr">
@@ -34875,7 +34931,7 @@
       </c>
       <c r="B1079" s="1" t="inlineStr">
         <is>
-          <t>[ˈmu.ʁu] 冲孔&lt;名&gt;</t>
+          <t>[ˈmu.ʁu] 拳打；拳头&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1079" s="1" t="inlineStr">
@@ -34885,7 +34941,7 @@
       </c>
       <c r="D1079" s="1" t="inlineStr">
         <is>
-          <t>冲孔</t>
+          <t>拳打；拳头</t>
         </is>
       </c>
       <c r="E1079" s="1" t="inlineStr">
@@ -34910,7 +34966,11 @@
           <t>目前&lt;副&gt;</t>
         </is>
       </c>
-      <c r="C1080" s="1" t="inlineStr"/>
+      <c r="C1080" s="1" t="inlineStr">
+        <is>
+          <t>/ak.twaˈmẽ.tʃi/</t>
+        </is>
+      </c>
       <c r="D1080" s="1" t="inlineStr">
         <is>
           <t>目前</t>
@@ -35639,7 +35699,7 @@
       </c>
       <c r="B1103" s="1" t="inlineStr">
         <is>
-          <t>[lẽˈsɔw] 片材&lt;名&gt;</t>
+          <t>[lẽˈsɔw] 床单&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1103" s="1" t="inlineStr">
@@ -35649,7 +35709,7 @@
       </c>
       <c r="D1103" s="1" t="inlineStr">
         <is>
-          <t>片材</t>
+          <t>床单</t>
         </is>
       </c>
       <c r="E1103" s="1" t="inlineStr">
@@ -36119,7 +36179,7 @@
       </c>
       <c r="B1118" s="1" t="inlineStr">
         <is>
-          <t>[suˈa(ʁ)] 汗水&lt;动&gt;</t>
+          <t>[suˈa(ʁ)] 出汗；流汗&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1118" s="1" t="inlineStr">
@@ -36129,7 +36189,7 @@
       </c>
       <c r="D1118" s="1" t="inlineStr">
         <is>
-          <t>汗水</t>
+          <t>出汗；流汗</t>
         </is>
       </c>
       <c r="E1118" s="1" t="inlineStr">
@@ -36343,7 +36403,7 @@
       </c>
       <c r="B1125" s="1" t="inlineStr">
         <is>
-          <t>[ˈkɔ.lu] 圈&lt;名&gt;</t>
+          <t>[ˈkɔ.lu] 怀；怀抱；膝上&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1125" s="1" t="inlineStr">
@@ -36353,7 +36413,7 @@
       </c>
       <c r="D1125" s="1" t="inlineStr">
         <is>
-          <t>圈</t>
+          <t>怀；怀抱；膝上</t>
         </is>
       </c>
       <c r="E1125" s="1" t="inlineStr">
@@ -36508,7 +36568,7 @@
       </c>
       <c r="C1130" s="1" t="inlineStr">
         <is>
-          <t>e.ˈlɛ.tɾi.kʊ</t>
+          <t>/e.ˈlɛ.tɾi.kʊ/</t>
         </is>
       </c>
       <c r="D1130" s="1" t="inlineStr">
@@ -37623,7 +37683,7 @@
       </c>
       <c r="B1165" s="1" t="inlineStr">
         <is>
-          <t>[foʁˈsa(ʁ)] 力&lt;动&gt;</t>
+          <t>[foʁˈsa(ʁ)] 强迫；强制&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1165" s="1" t="inlineStr">
@@ -37633,7 +37693,7 @@
       </c>
       <c r="D1165" s="1" t="inlineStr">
         <is>
-          <t>力</t>
+          <t>强迫；强制</t>
         </is>
       </c>
       <c r="E1165" s="1" t="inlineStr">
@@ -37911,7 +37971,7 @@
       </c>
       <c r="B1174" s="1" t="inlineStr">
         <is>
-          <t>[ˈpɛʁ.kɐ] 想念&lt;名&gt;</t>
+          <t>[ˈpɛʁ.kɐ] 损失&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1174" s="1" t="inlineStr">
@@ -37921,7 +37981,7 @@
       </c>
       <c r="D1174" s="1" t="inlineStr">
         <is>
-          <t>想念</t>
+          <t>损失</t>
         </is>
       </c>
       <c r="E1174" s="1" t="inlineStr">
@@ -38647,7 +38707,7 @@
       </c>
       <c r="B1197" s="1" t="inlineStr">
         <is>
-          <t>[ˈpɾa.sɐ] 正方形&lt;名&gt;</t>
+          <t>[ˈpɾa.sɐ] 广场&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1197" s="1" t="inlineStr">
@@ -38657,7 +38717,7 @@
       </c>
       <c r="D1197" s="1" t="inlineStr">
         <is>
-          <t>正方形</t>
+          <t>广场</t>
         </is>
       </c>
       <c r="E1197" s="1" t="inlineStr">
@@ -38716,7 +38776,7 @@
       </c>
       <c r="C1199" s="1" t="inlineStr">
         <is>
-          <t>a.ˈtʃi.vʊ</t>
+          <t>/a.ˈtʃi.vʊ/</t>
         </is>
       </c>
       <c r="D1199" s="1" t="inlineStr">
@@ -38871,7 +38931,7 @@
       </c>
       <c r="B1204" s="1" t="inlineStr">
         <is>
-          <t>[ʁe.koʁ.daˈsɐ̃w̃] 纪念品&lt;名&gt;</t>
+          <t>[/ʁe.koʁ.daˈsɐ̃w̃/] 回忆；纪念品&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1204" s="1" t="inlineStr">
@@ -38881,7 +38941,7 @@
       </c>
       <c r="D1204" s="1" t="inlineStr">
         <is>
-          <t>纪念品</t>
+          <t>回忆；纪念品&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1204" s="1" t="inlineStr">
@@ -39164,7 +39224,7 @@
       </c>
       <c r="C1213" s="1" t="inlineStr">
         <is>
-          <t>de.si.ˈdʒi.ɾãʊ̃</t>
+          <t>/de.si.ˈdʒi.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D1213" s="1" t="inlineStr">
@@ -39223,7 +39283,7 @@
       </c>
       <c r="B1215" s="1" t="inlineStr">
         <is>
-          <t>[kes.t͡ʃi.oˈna(ʁ)] 问题&lt;动&gt;</t>
+          <t>[kes.t͡ʃi.oˈna(ʁ)] 质疑；提问&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1215" s="1" t="inlineStr">
@@ -39233,7 +39293,7 @@
       </c>
       <c r="D1215" s="1" t="inlineStr">
         <is>
-          <t>问题</t>
+          <t>质疑；提问</t>
         </is>
       </c>
       <c r="E1215" s="1" t="inlineStr">
@@ -39383,7 +39443,7 @@
       </c>
       <c r="B1220" s="1" t="inlineStr">
         <is>
-          <t>[ˈmõ.nɐ] 莫娜&lt;名&gt;</t>
+          <t>[/ˈmõ.nɐ/] 母猴；雌性猴子&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1220" s="1" t="inlineStr">
@@ -39393,7 +39453,7 @@
       </c>
       <c r="D1220" s="1" t="inlineStr">
         <is>
-          <t>莫娜</t>
+          <t>母猴；雌性猴子</t>
         </is>
       </c>
       <c r="E1220" s="1" t="inlineStr">
@@ -39479,7 +39539,7 @@
       </c>
       <c r="B1223" s="1" t="inlineStr">
         <is>
-          <t>[nojˈva.du] 参与度&lt;名&gt;</t>
+          <t>[nojˈva.du] 订婚&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1223" s="1" t="inlineStr">
@@ -39489,7 +39549,7 @@
       </c>
       <c r="D1223" s="1" t="inlineStr">
         <is>
-          <t>参与度</t>
+          <t>订婚</t>
         </is>
       </c>
       <c r="E1223" s="1" t="inlineStr">
@@ -39607,7 +39667,7 @@
       </c>
       <c r="B1227" s="1" t="inlineStr">
         <is>
-          <t>[ˈd͡ʒi.kɐ] 小费&lt;名&gt;</t>
+          <t>[ˈd͡ʒi.kɐ] 提示；窍门&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1227" s="1" t="inlineStr">
@@ -39617,7 +39677,7 @@
       </c>
       <c r="D1227" s="1" t="inlineStr">
         <is>
-          <t>小费</t>
+          <t>提示；窍门</t>
         </is>
       </c>
       <c r="E1227" s="1" t="inlineStr">
@@ -39703,7 +39763,7 @@
       </c>
       <c r="B1230" s="1" t="inlineStr">
         <is>
-          <t>[pɐ̃ˈka.dɐ] 吹&lt;名&gt;</t>
+          <t>[pɐ̃ˈka.dɐ] 打击；击打；一击&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1230" s="1" t="inlineStr">
@@ -39713,7 +39773,7 @@
       </c>
       <c r="D1230" s="1" t="inlineStr">
         <is>
-          <t>吹</t>
+          <t>打击；击打；一击</t>
         </is>
       </c>
       <c r="E1230" s="1" t="inlineStr">
@@ -39735,7 +39795,7 @@
       </c>
       <c r="B1231" s="1" t="inlineStr">
         <is>
-          <t>[ẽ.fiˈa(ʁ)] 线程&lt;动&gt;</t>
+          <t>[ẽ.fiˈa(ʁ)] 穿入；塞进；穿线&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1231" s="1" t="inlineStr">
@@ -39745,7 +39805,7 @@
       </c>
       <c r="D1231" s="1" t="inlineStr">
         <is>
-          <t>线程</t>
+          <t>穿入；塞进；穿线</t>
         </is>
       </c>
       <c r="E1231" s="1" t="inlineStr">
@@ -39767,7 +39827,7 @@
       </c>
       <c r="B1232" s="1" t="inlineStr">
         <is>
-          <t>[kaˈɡa(ʁ)] 狗屎&lt;动&gt;</t>
+          <t>[kaˈɡa(ʁ)] 拉屎；排便&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1232" s="1" t="inlineStr">
@@ -39777,7 +39837,7 @@
       </c>
       <c r="D1232" s="1" t="inlineStr">
         <is>
-          <t>狗屎</t>
+          <t>拉屎；排便</t>
         </is>
       </c>
       <c r="E1232" s="1" t="inlineStr">
@@ -40188,7 +40248,7 @@
       </c>
       <c r="C1245" s="1" t="inlineStr">
         <is>
-          <t>fu.ˈʒi.ɾãʊ̃</t>
+          <t>/fu.ˈʒi.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D1245" s="1" t="inlineStr">
@@ -40314,7 +40374,11 @@
           <t>高速公路&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C1249" s="1" t="inlineStr"/>
+      <c r="C1249" s="1" t="inlineStr">
+        <is>
+          <t>/aw.tu.esˈtɾa.dɐ/</t>
+        </is>
+      </c>
       <c r="D1249" s="1" t="inlineStr">
         <is>
           <t>高速公路</t>
@@ -40467,7 +40531,7 @@
       </c>
       <c r="B1254" s="1" t="inlineStr">
         <is>
-          <t>[poˈtẽ.sjɐ] 电源&lt;名&gt;</t>
+          <t>[poˈtẽ.sjɐ] 力量；功率；威力；强国&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1254" s="1" t="inlineStr">
@@ -40477,7 +40541,7 @@
       </c>
       <c r="D1254" s="1" t="inlineStr">
         <is>
-          <t>电源</t>
+          <t>力量；功率；威力；强国</t>
         </is>
       </c>
       <c r="E1254" s="1" t="inlineStr">
@@ -40504,7 +40568,7 @@
       </c>
       <c r="C1255" s="1" t="inlineStr">
         <is>
-          <t>ˈvo.ʊ</t>
+          <t>/ˈvo.ʊ/</t>
         </is>
       </c>
       <c r="D1255" s="1" t="inlineStr">
@@ -40947,7 +41011,7 @@
       </c>
       <c r="B1269" s="1" t="inlineStr">
         <is>
-          <t>[puˈzɛ.ɾɐ̃w̃] 把&lt;动&gt;</t>
+          <t>[puˈzɛ.ɾɐ̃w̃] 放；放置&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1269" s="1" t="inlineStr">
@@ -40957,7 +41021,7 @@
       </c>
       <c r="D1269" s="1" t="inlineStr">
         <is>
-          <t>把</t>
+          <t>放；放置</t>
         </is>
       </c>
       <c r="E1269" s="1" t="inlineStr">
@@ -41144,7 +41208,7 @@
       </c>
       <c r="C1275" s="1" t="inlineStr">
         <is>
-          <t>mã.ˈda.ɾãʊ̃</t>
+          <t>/mã.ˈda.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D1275" s="1" t="inlineStr">
@@ -41272,7 +41336,7 @@
       </c>
       <c r="C1279" s="1" t="inlineStr">
         <is>
-          <t>fa.le.ˈsi.dʊ</t>
+          <t>/fa.le.ˈsi.dʊ/</t>
         </is>
       </c>
       <c r="D1279" s="1" t="inlineStr">
@@ -41622,7 +41686,11 @@
           <t>短信&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C1290" s="1" t="inlineStr"/>
+      <c r="C1290" s="1" t="inlineStr">
+        <is>
+          <t>/sms/</t>
+        </is>
+      </c>
       <c r="D1290" s="1" t="inlineStr">
         <is>
           <t>短信</t>
@@ -41746,7 +41814,11 @@
           <t>夫人&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C1294" s="1" t="inlineStr"/>
+      <c r="C1294" s="1" t="inlineStr">
+        <is>
+          <t>/sẽˈɲɔ.ɾɐ/</t>
+        </is>
+      </c>
       <c r="D1294" s="1" t="inlineStr">
         <is>
           <t>夫人</t>
@@ -41840,7 +41912,7 @@
       </c>
       <c r="C1297" s="1" t="inlineStr">
         <is>
-          <t>a.tu.ˈax</t>
+          <t>/a.tu.ˈax/</t>
         </is>
       </c>
       <c r="D1297" s="1" t="inlineStr">
@@ -41867,7 +41939,7 @@
       </c>
       <c r="B1298" s="1" t="inlineStr">
         <is>
-          <t>[oˈta.ɾju] 吸盘&lt;形&gt;</t>
+          <t>[oˈta.ɾju] 傻瓜；笨蛋&lt;形&gt;</t>
         </is>
       </c>
       <c r="C1298" s="1" t="inlineStr">
@@ -41877,7 +41949,7 @@
       </c>
       <c r="D1298" s="1" t="inlineStr">
         <is>
-          <t>吸盘</t>
+          <t>傻瓜；笨蛋</t>
         </is>
       </c>
       <c r="E1298" s="1" t="inlineStr">
@@ -42283,7 +42355,7 @@
       </c>
       <c r="B1311" s="1" t="inlineStr">
         <is>
-          <t>[o.bɾiˈɡa(ʁ)] 义务&lt;动&gt;</t>
+          <t>[o.bɾiˈɡa(ʁ)] 强迫；迫使&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1311" s="1" t="inlineStr">
@@ -42293,7 +42365,7 @@
       </c>
       <c r="D1311" s="1" t="inlineStr">
         <is>
-          <t>义务</t>
+          <t>强迫；迫使</t>
         </is>
       </c>
       <c r="E1311" s="1" t="inlineStr">
@@ -42315,7 +42387,7 @@
       </c>
       <c r="B1312" s="1" t="inlineStr">
         <is>
-          <t>[a.poˈzẽ.tu] 房间&lt;名&gt;</t>
+          <t>[a.poˈzẽ.tu] 房间；住所&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1312" s="1" t="inlineStr">
@@ -42325,7 +42397,7 @@
       </c>
       <c r="D1312" s="1" t="inlineStr">
         <is>
-          <t>房间</t>
+          <t>房间；住所</t>
         </is>
       </c>
       <c r="E1312" s="1" t="inlineStr">
@@ -43019,7 +43091,7 @@
       </c>
       <c r="B1334" s="1" t="inlineStr">
         <is>
-          <t>[ʁe.zeʁˈva(ʁ)] 书&lt;动&gt;</t>
+          <t>[ʁe.zeʁˈva(ʁ)] 预订；保留&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1334" s="1" t="inlineStr">
@@ -43029,7 +43101,7 @@
       </c>
       <c r="D1334" s="1" t="inlineStr">
         <is>
-          <t>书</t>
+          <t>预订；保留</t>
         </is>
       </c>
       <c r="E1334" s="1" t="inlineStr">
@@ -43307,7 +43379,7 @@
       </c>
       <c r="B1343" s="1" t="inlineStr">
         <is>
-          <t>[a.luˈɡa(ʁ)] 租金&lt;动&gt;</t>
+          <t>[a.luˈɡa(ʁ)] 租；出租；租用&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1343" s="1" t="inlineStr">
@@ -43317,7 +43389,7 @@
       </c>
       <c r="D1343" s="1" t="inlineStr">
         <is>
-          <t>租金</t>
+          <t>租；出租；租用</t>
         </is>
       </c>
       <c r="E1343" s="1" t="inlineStr">
@@ -43467,7 +43539,7 @@
       </c>
       <c r="B1348" s="1" t="inlineStr">
         <is>
-          <t>[ˈba.tɐ] 击败&lt;名&gt;</t>
+          <t>[ˈba.tɐ] 罩衫；工作服&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1348" s="1" t="inlineStr">
@@ -43477,7 +43549,7 @@
       </c>
       <c r="D1348" s="1" t="inlineStr">
         <is>
-          <t>击败</t>
+          <t>罩衫；工作服</t>
         </is>
       </c>
       <c r="E1348" s="1" t="inlineStr">
@@ -43851,7 +43923,7 @@
       </c>
       <c r="B1360" s="1" t="inlineStr">
         <is>
-          <t>[ˈso.ku] 冲孔&lt;名&gt;</t>
+          <t>[ˈso.ku] 拳打；一拳&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1360" s="1" t="inlineStr">
@@ -43861,7 +43933,7 @@
       </c>
       <c r="D1360" s="1" t="inlineStr">
         <is>
-          <t>冲孔</t>
+          <t>拳打；一拳</t>
         </is>
       </c>
       <c r="E1360" s="1" t="inlineStr">
@@ -43883,7 +43955,7 @@
       </c>
       <c r="B1361" s="1" t="inlineStr">
         <is>
-          <t>[do(w)ˈɾa.du] 金色&lt;名&gt;</t>
+          <t>[/do(w)ˈɾa.du/] 金色的&lt;形&gt;；金鲷鱼&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1361" s="1" t="inlineStr">
@@ -43893,7 +43965,7 @@
       </c>
       <c r="D1361" s="1" t="inlineStr">
         <is>
-          <t>金色</t>
+          <t>金色的&lt;形&gt;；金鲷鱼&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1361" s="1" t="inlineStr">
@@ -44112,7 +44184,7 @@
       </c>
       <c r="C1368" s="1" t="inlineStr">
         <is>
-          <t>tʃi.ˈɾa.ɾãʊ̃</t>
+          <t>/tʃi.ˈɾa.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D1368" s="1" t="inlineStr">
@@ -44395,17 +44467,17 @@
       </c>
       <c r="B1377" s="1" t="inlineStr">
         <is>
-          <t>[u.ˈza.ɾãʊ̃] 使用过的&lt;动&gt;</t>
+          <t>[u.ˈza.ɾãʊ̃] 使用了&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1377" s="1" t="inlineStr">
         <is>
-          <t>u.ˈza.ɾãʊ̃</t>
+          <t>/u.ˈza.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D1377" s="1" t="inlineStr">
         <is>
-          <t>使用过的</t>
+          <t>使用了</t>
         </is>
       </c>
       <c r="E1377" s="1" t="inlineStr">
@@ -44619,7 +44691,7 @@
       </c>
       <c r="B1384" s="1" t="inlineStr">
         <is>
-          <t>[ẽ.kaˈɾa(ʁ)] 脸&lt;动&gt;</t>
+          <t>[ẽ.kaˈɾa(ʁ)] 直视；正视；面对&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1384" s="1" t="inlineStr">
@@ -44629,7 +44701,7 @@
       </c>
       <c r="D1384" s="1" t="inlineStr">
         <is>
-          <t>脸</t>
+          <t>直视；正视；面对</t>
         </is>
       </c>
       <c r="E1384" s="1" t="inlineStr">
@@ -44651,7 +44723,7 @@
       </c>
       <c r="B1385" s="1" t="inlineStr">
         <is>
-          <t>[eˈɾɐ̃.sɐ] 继承&lt;名&gt;</t>
+          <t>[/eˈɾɐ̃.sɐ/] 遗产&lt;名&gt;；继承&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1385" s="1" t="inlineStr">
@@ -44661,7 +44733,7 @@
       </c>
       <c r="D1385" s="1" t="inlineStr">
         <is>
-          <t>继承</t>
+          <t>遗产&lt;名&gt;；继承&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1385" s="1" t="inlineStr">
@@ -44683,17 +44755,17 @@
       </c>
       <c r="B1386" s="1" t="inlineStr">
         <is>
-          <t>[pex.se.ˈbe.ɾãʊ̃] 实现了&lt;动&gt;</t>
+          <t>[pex.se.ˈbe.ɾãʊ̃] 明白了；理解了&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1386" s="1" t="inlineStr">
         <is>
-          <t>pex.se.ˈbe.ɾãʊ̃</t>
+          <t>/pex.se.ˈbe.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D1386" s="1" t="inlineStr">
         <is>
-          <t>实现了</t>
+          <t>明白了；理解了</t>
         </is>
       </c>
       <c r="E1386" s="1" t="inlineStr">
@@ -45771,7 +45843,7 @@
       </c>
       <c r="B1420" s="1" t="inlineStr">
         <is>
-          <t>[posˈtaw] 明信片&lt;名&gt;</t>
+          <t>[posˈtaw] 邮政的；明信片&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1420" s="1" t="inlineStr">
@@ -45781,7 +45853,7 @@
       </c>
       <c r="D1420" s="1" t="inlineStr">
         <is>
-          <t>明信片</t>
+          <t>邮政的；明信片</t>
         </is>
       </c>
       <c r="E1420" s="1" t="inlineStr">
@@ -45902,7 +45974,11 @@
           <t>夫人&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C1424" s="1" t="inlineStr"/>
+      <c r="C1424" s="1" t="inlineStr">
+        <is>
+          <t>/sẽˈɲɔ.ɾɐ/</t>
+        </is>
+      </c>
       <c r="D1424" s="1" t="inlineStr">
         <is>
           <t>夫人</t>
@@ -46028,7 +46104,7 @@
       </c>
       <c r="C1428" s="1" t="inlineStr">
         <is>
-          <t>dɾa.ˈgõỹs</t>
+          <t>/dɾa.ˈgõỹs/</t>
         </is>
       </c>
       <c r="D1428" s="1" t="inlineStr">
@@ -46375,7 +46451,7 @@
       </c>
       <c r="B1439" s="1" t="inlineStr">
         <is>
-          <t>[ĩˈvɛ(j)s] 相反&lt;名&gt;</t>
+          <t>[/ĩˈvɛ(j)s/] 反而；相反地（ao invés de = 而不是）&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1439" s="1" t="inlineStr">
@@ -46385,7 +46461,7 @@
       </c>
       <c r="D1439" s="1" t="inlineStr">
         <is>
-          <t>相反</t>
+          <t>反而；相反地（ao invés de = 而不是）</t>
         </is>
       </c>
       <c r="E1439" s="1" t="inlineStr">
@@ -46439,7 +46515,7 @@
       </c>
       <c r="B1441" s="1" t="inlineStr">
         <is>
-          <t>[po.li.siˈa(ʁ)] 警察&lt;名&gt;</t>
+          <t>[po.li.siˈa(ʁ)] 维持治安；巡逻&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1441" s="1" t="inlineStr">
@@ -46449,7 +46525,7 @@
       </c>
       <c r="D1441" s="1" t="inlineStr">
         <is>
-          <t>警察</t>
+          <t>维持治安；巡逻</t>
         </is>
       </c>
       <c r="E1441" s="1" t="inlineStr">
@@ -46503,7 +46579,7 @@
       </c>
       <c r="B1443" s="1" t="inlineStr">
         <is>
-          <t>[is.tɾaˈɡa.du] 被宠坏的&lt;形&gt;</t>
+          <t>[is.tɾaˈɡa.du] 损坏的；坏了的&lt;形&gt;</t>
         </is>
       </c>
       <c r="C1443" s="1" t="inlineStr">
@@ -46513,7 +46589,7 @@
       </c>
       <c r="D1443" s="1" t="inlineStr">
         <is>
-          <t>被宠坏的</t>
+          <t>损坏的；坏了的</t>
         </is>
       </c>
       <c r="E1443" s="1" t="inlineStr">
@@ -46567,7 +46643,7 @@
       </c>
       <c r="B1445" s="1" t="inlineStr">
         <is>
-          <t>[ˈku.bɐ] 增值税&lt;名&gt;</t>
+          <t>[ˈku.bɐ] 洗涤槽；水槽；盆&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1445" s="1" t="inlineStr">
@@ -46577,7 +46653,7 @@
       </c>
       <c r="D1445" s="1" t="inlineStr">
         <is>
-          <t>增值税</t>
+          <t>洗涤槽；水槽；盆</t>
         </is>
       </c>
       <c r="E1445" s="1" t="inlineStr">
@@ -46983,7 +47059,7 @@
       </c>
       <c r="B1458" s="1" t="inlineStr">
         <is>
-          <t>[ˈkɔ.kɐ] 可乐&lt;名&gt;</t>
+          <t>[ˈkɔ.kɐ] 古柯；古柯叶&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1458" s="1" t="inlineStr">
@@ -46993,7 +47069,7 @@
       </c>
       <c r="D1458" s="1" t="inlineStr">
         <is>
-          <t>可乐</t>
+          <t>古柯；古柯叶</t>
         </is>
       </c>
       <c r="E1458" s="1" t="inlineStr">
@@ -47338,7 +47414,11 @@
           <t>蜜月&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C1469" s="1" t="inlineStr"/>
+      <c r="C1469" s="1" t="inlineStr">
+        <is>
+          <t>/ˈlu.ɐ dʒi ˈmɛw/</t>
+        </is>
+      </c>
       <c r="D1469" s="1" t="inlineStr">
         <is>
           <t>蜜月</t>
@@ -47427,7 +47507,7 @@
       </c>
       <c r="B1472" s="1" t="inlineStr">
         <is>
-          <t>[kõ.suwˈtɔ.ɾju] 办公室&lt;名&gt;</t>
+          <t>[kõ.suwˈtɔ.ɾju] 诊所；诊室&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1472" s="1" t="inlineStr">
@@ -47437,7 +47517,7 @@
       </c>
       <c r="D1472" s="1" t="inlineStr">
         <is>
-          <t>办公室</t>
+          <t>诊所；诊室</t>
         </is>
       </c>
       <c r="E1472" s="1" t="inlineStr">
@@ -47656,7 +47736,7 @@
       </c>
       <c r="C1479" s="1" t="inlineStr">
         <is>
-          <t>tɾãs.fe.ˈɾi.dʊ</t>
+          <t>/tɾãs.fe.ˈɾi.dʊ/</t>
         </is>
       </c>
       <c r="D1479" s="1" t="inlineStr">
@@ -47715,7 +47795,7 @@
       </c>
       <c r="B1481" s="1" t="inlineStr">
         <is>
-          <t>[ˈsu.bɐ] 上去&lt;名&gt;</t>
+          <t>[/ˈsu.bɐ/] subir的虚拟式/命令式变位形式&lt;动&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1481" s="1" t="inlineStr">
@@ -47725,7 +47805,7 @@
       </c>
       <c r="D1481" s="1" t="inlineStr">
         <is>
-          <t>上去</t>
+          <t>subir的虚拟式/命令式变位形式&lt;动&gt;</t>
         </is>
       </c>
       <c r="E1481" s="1" t="inlineStr">
@@ -47875,7 +47955,7 @@
       </c>
       <c r="B1486" s="1" t="inlineStr">
         <is>
-          <t>[ˈmuw.tɐ] 很好&lt;名&gt;</t>
+          <t>[/ˈmuw.tɐ/] 罚款&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1486" s="1" t="inlineStr">
@@ -47885,7 +47965,7 @@
       </c>
       <c r="D1486" s="1" t="inlineStr">
         <is>
-          <t>很好</t>
+          <t>罚款&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1486" s="1" t="inlineStr">
@@ -48099,7 +48179,7 @@
       </c>
       <c r="B1493" s="1" t="inlineStr">
         <is>
-          <t>[fu.ziˈle(j).ɾu] 海洋&lt;名&gt;</t>
+          <t>[/fu.ziˈle(j).ɾu/] 海军陆战队员&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1493" s="1" t="inlineStr">
@@ -48109,7 +48189,7 @@
       </c>
       <c r="D1493" s="1" t="inlineStr">
         <is>
-          <t>海洋</t>
+          <t>海军陆战队员&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1493" s="1" t="inlineStr">
@@ -48131,7 +48211,7 @@
       </c>
       <c r="B1494" s="1" t="inlineStr">
         <is>
-          <t>[blo.kiˈa(ʁ)] 块&lt;动&gt;</t>
+          <t>[/blo.kiˈa(ʁ)/] 阻挡；封锁&lt;动&gt;&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1494" s="1" t="inlineStr">
@@ -48141,7 +48221,7 @@
       </c>
       <c r="D1494" s="1" t="inlineStr">
         <is>
-          <t>块</t>
+          <t>阻挡；封锁&lt;动&gt;</t>
         </is>
       </c>
       <c r="E1494" s="1" t="inlineStr">
@@ -48355,7 +48435,7 @@
       </c>
       <c r="B1501" s="1" t="inlineStr">
         <is>
-          <t>[ˈpo.dɾi] 腐烂的&lt;名&gt;</t>
+          <t>[/ˈpo.dɾi/] 腐烂的&lt;形&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1501" s="1" t="inlineStr">
@@ -48365,7 +48445,7 @@
       </c>
       <c r="D1501" s="1" t="inlineStr">
         <is>
-          <t>腐烂的</t>
+          <t>腐烂的&lt;形&gt;</t>
         </is>
       </c>
       <c r="E1501" s="1" t="inlineStr">
@@ -48387,7 +48467,7 @@
       </c>
       <c r="B1502" s="1" t="inlineStr">
         <is>
-          <t>[ẽˈkɔs.tɐ] 坡度&lt;名&gt;</t>
+          <t>[/ẽˈkɔs.tɐ/] 山坡&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1502" s="1" t="inlineStr">
@@ -48397,7 +48477,7 @@
       </c>
       <c r="D1502" s="1" t="inlineStr">
         <is>
-          <t>坡度</t>
+          <t>山坡&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1502" s="1" t="inlineStr">
@@ -48552,7 +48632,7 @@
       </c>
       <c r="C1507" s="1" t="inlineStr">
         <is>
-          <t>kõ.ɲe.ˈse.ɾãʊ̃</t>
+          <t>/kõ.ɲe.ˈse.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D1507" s="1" t="inlineStr">
@@ -48744,7 +48824,7 @@
       </c>
       <c r="C1513" s="1" t="inlineStr">
         <is>
-          <t>fe.ˈʃow</t>
+          <t>/fe.ˈʃow/</t>
         </is>
       </c>
       <c r="D1513" s="1" t="inlineStr">
@@ -48803,7 +48883,7 @@
       </c>
       <c r="B1515" s="1" t="inlineStr">
         <is>
-          <t>[ˈʁõ.dɐ] 圆形&lt;名&gt;</t>
+          <t>[ˈʁõ.dɐ] 巡逻；巡逻队&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1515" s="1" t="inlineStr">
@@ -48813,7 +48893,7 @@
       </c>
       <c r="D1515" s="1" t="inlineStr">
         <is>
-          <t>圆形</t>
+          <t>巡逻；巡逻队</t>
         </is>
       </c>
       <c r="E1515" s="1" t="inlineStr">
@@ -49190,7 +49270,11 @@
           <t>也&lt;副&gt;</t>
         </is>
       </c>
-      <c r="C1527" s="1" t="inlineStr"/>
+      <c r="C1527" s="1" t="inlineStr">
+        <is>
+          <t>/tɐ̃ˈbẽj/</t>
+        </is>
+      </c>
       <c r="D1527" s="1" t="inlineStr">
         <is>
           <t>也</t>
@@ -49279,7 +49363,7 @@
       </c>
       <c r="B1530" s="1" t="inlineStr">
         <is>
-          <t>[is.koˈlaʁ] 学校&lt;形&gt;</t>
+          <t>[is.koˈlaʁ] 学校的；学龄的&lt;形&gt;</t>
         </is>
       </c>
       <c r="C1530" s="1" t="inlineStr">
@@ -49289,7 +49373,7 @@
       </c>
       <c r="D1530" s="1" t="inlineStr">
         <is>
-          <t>学校</t>
+          <t>学校的；学龄的</t>
         </is>
       </c>
       <c r="E1530" s="1" t="inlineStr">
@@ -49343,7 +49427,7 @@
       </c>
       <c r="B1532" s="1" t="inlineStr">
         <is>
-          <t>[ˈla.su] 循环&lt;名&gt;</t>
+          <t>[/ˈla.su/] 绳结；圈套；花边&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1532" s="1" t="inlineStr">
@@ -49353,7 +49437,7 @@
       </c>
       <c r="D1532" s="1" t="inlineStr">
         <is>
-          <t>循环</t>
+          <t>绳结；圈套；花边&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1532" s="1" t="inlineStr">
@@ -49663,7 +49747,7 @@
       </c>
       <c r="B1542" s="1" t="inlineStr">
         <is>
-          <t>[tɨ.lɨˈfɔ.ni.ku] 电话&lt;形&gt;</t>
+          <t>[tɨ.lɨˈfɔ.ni.ku] 电话的&lt;形&gt;</t>
         </is>
       </c>
       <c r="C1542" s="1" t="inlineStr">
@@ -49673,7 +49757,7 @@
       </c>
       <c r="D1542" s="1" t="inlineStr">
         <is>
-          <t>电话</t>
+          <t>电话的</t>
         </is>
       </c>
       <c r="E1542" s="1" t="inlineStr">
@@ -49855,7 +49939,7 @@
       </c>
       <c r="B1548" s="1" t="inlineStr">
         <is>
-          <t>[aw.veˈʒa(ʁ)] 漂白剂&lt;动&gt;</t>
+          <t>[aw.veˈʒa(ʁ)] 瞄准；射击；以…为目标&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1548" s="1" t="inlineStr">
@@ -49865,7 +49949,7 @@
       </c>
       <c r="D1548" s="1" t="inlineStr">
         <is>
-          <t>漂白剂</t>
+          <t>瞄准；射击；以…为目标</t>
         </is>
       </c>
       <c r="E1548" s="1" t="inlineStr">
@@ -49986,7 +50070,11 @@
           <t>保龄球&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C1552" s="1" t="inlineStr"/>
+      <c r="C1552" s="1" t="inlineStr">
+        <is>
+          <t>/ˈbəʊ.lɪŋ/</t>
+        </is>
+      </c>
       <c r="D1552" s="1" t="inlineStr">
         <is>
           <t>保龄球</t>
@@ -50331,7 +50419,7 @@
       </c>
       <c r="B1563" s="1" t="inlineStr">
         <is>
-          <t>[ẽ.ɡuˈli(ʁ)] 燕子&lt;动&gt;</t>
+          <t>[ẽ.ɡuˈli(ʁ)] 吞下；吞咽&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1563" s="1" t="inlineStr">
@@ -50341,7 +50429,7 @@
       </c>
       <c r="D1563" s="1" t="inlineStr">
         <is>
-          <t>燕子</t>
+          <t>吞下；吞咽</t>
         </is>
       </c>
       <c r="E1563" s="1" t="inlineStr">
@@ -50587,7 +50675,7 @@
       </c>
       <c r="B1571" s="1" t="inlineStr">
         <is>
-          <t>[ˈaʁ.kɐ] 方舟&lt;名&gt;</t>
+          <t>[/ˈaʁ.kɐ/] 箱子；柜子（也指方舟）&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1571" s="1" t="inlineStr">
@@ -50597,7 +50685,7 @@
       </c>
       <c r="D1571" s="1" t="inlineStr">
         <is>
-          <t>方舟</t>
+          <t>箱子；柜子（也指方舟）</t>
         </is>
       </c>
       <c r="E1571" s="1" t="inlineStr">
@@ -50619,7 +50707,7 @@
       </c>
       <c r="B1572" s="1" t="inlineStr">
         <is>
-          <t>[aʁˈma(ʁ)] 手臂&lt;动&gt;</t>
+          <t>[aʁˈma(ʁ)] 武装；装配；架设&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1572" s="1" t="inlineStr">
@@ -50629,7 +50717,7 @@
       </c>
       <c r="D1572" s="1" t="inlineStr">
         <is>
-          <t>手臂</t>
+          <t>武装；装配；架设</t>
         </is>
       </c>
       <c r="E1572" s="1" t="inlineStr">
@@ -50747,7 +50835,7 @@
       </c>
       <c r="B1576" s="1" t="inlineStr">
         <is>
-          <t>[ˈmi.sɐ] 质量&lt;名&gt;</t>
+          <t>[ˈmi.sɐ] 弥撒&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1576" s="1" t="inlineStr">
@@ -50757,7 +50845,7 @@
       </c>
       <c r="D1576" s="1" t="inlineStr">
         <is>
-          <t>质量</t>
+          <t>弥撒</t>
         </is>
       </c>
       <c r="E1576" s="1" t="inlineStr">
@@ -52379,7 +52467,7 @@
       </c>
       <c r="B1627" s="1" t="inlineStr">
         <is>
-          <t>[is.t͡ʃi.maˈsɐ̃w̃] 宠物&lt;名&gt;</t>
+          <t>[/is.t͡ʃi.maˈsɐ̃w̃/] 尊重；尊敬&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1627" s="1" t="inlineStr">
@@ -52389,7 +52477,7 @@
       </c>
       <c r="D1627" s="1" t="inlineStr">
         <is>
-          <t>宠物</t>
+          <t>尊重；尊敬&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1627" s="1" t="inlineStr">
@@ -52670,7 +52758,11 @@
           <t>汉&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C1636" s="1" t="inlineStr"/>
+      <c r="C1636" s="1" t="inlineStr">
+        <is>
+          <t>/hɐ̃/</t>
+        </is>
+      </c>
       <c r="D1636" s="1" t="inlineStr">
         <is>
           <t>汉</t>
@@ -53052,7 +53144,7 @@
       </c>
       <c r="C1648" s="1" t="inlineStr">
         <is>
-          <t>xe.ˈtʃi.ɾʊ</t>
+          <t>/xe.ˈtʃi.ɾʊ/</t>
         </is>
       </c>
       <c r="D1648" s="1" t="inlineStr">
@@ -53180,7 +53272,7 @@
       </c>
       <c r="C1652" s="1" t="inlineStr">
         <is>
-          <t>ˈvi.ẽỹ</t>
+          <t>/ˈvi.ẽỹ/</t>
         </is>
       </c>
       <c r="D1652" s="1" t="inlineStr">
@@ -53660,7 +53752,7 @@
       </c>
       <c r="C1667" s="1" t="inlineStr">
         <is>
-          <t>pɾo.tʃe.ˈtox</t>
+          <t>/pɾo.tʃe.ˈtox/</t>
         </is>
       </c>
       <c r="D1667" s="1" t="inlineStr">
@@ -54076,7 +54168,7 @@
       </c>
       <c r="C1680" s="1" t="inlineStr">
         <is>
-          <t>a.tʃi.ˈvax</t>
+          <t>/a.tʃi.ˈvax/</t>
         </is>
       </c>
       <c r="D1680" s="1" t="inlineStr">
@@ -54236,7 +54328,7 @@
       </c>
       <c r="C1685" s="1" t="inlineStr">
         <is>
-          <t>pa.ˈɾa.ɾãʊ̃</t>
+          <t>/pa.ˈɾa.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D1685" s="1" t="inlineStr">
@@ -54327,7 +54419,7 @@
       </c>
       <c r="B1688" s="1" t="inlineStr">
         <is>
-          <t>[oʁ.deˈna(ʁ)] 订单&lt;动&gt;</t>
+          <t>[/oʁ.deˈna(ʁ)/] 命令&lt;动&gt;；整理&lt;动&gt;&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C1688" s="1" t="inlineStr">
@@ -54337,7 +54429,7 @@
       </c>
       <c r="D1688" s="1" t="inlineStr">
         <is>
-          <t>订单</t>
+          <t>命令&lt;动&gt;；整理&lt;动&gt;</t>
         </is>
       </c>
       <c r="E1688" s="1" t="inlineStr">
@@ -54359,7 +54451,7 @@
       </c>
       <c r="B1689" s="1" t="inlineStr">
         <is>
-          <t>[ˈtɔʁ.tɐ] 馅饼&lt;名&gt;</t>
+          <t>[/ˈtɔʁ.tɐ/] 蛋糕；夹心蛋糕&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1689" s="1" t="inlineStr">
@@ -54369,7 +54461,7 @@
       </c>
       <c r="D1689" s="1" t="inlineStr">
         <is>
-          <t>馅饼</t>
+          <t>蛋糕；夹心蛋糕&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1689" s="1" t="inlineStr">
@@ -54460,7 +54552,7 @@
       </c>
       <c r="C1692" s="1" t="inlineStr">
         <is>
-          <t>tʃĩ.ˈɲã.mʊs</t>
+          <t>/tʃĩ.ˈɲã.mʊs/</t>
         </is>
       </c>
       <c r="D1692" s="1" t="inlineStr">
@@ -54583,7 +54675,7 @@
       </c>
       <c r="B1696" s="1" t="inlineStr">
         <is>
-          <t>[pi.loˈta(ʁ)] 飞行员&lt;动&gt;</t>
+          <t>[pi.loˈta(ʁ)] 驾驶；操纵（飞机等）&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1696" s="1" t="inlineStr">
@@ -54593,7 +54685,7 @@
       </c>
       <c r="D1696" s="1" t="inlineStr">
         <is>
-          <t>飞行员</t>
+          <t>驾驶；操纵（飞机等）</t>
         </is>
       </c>
       <c r="E1696" s="1" t="inlineStr">
@@ -54778,10 +54870,14 @@
           <t>市长&lt;形&gt;</t>
         </is>
       </c>
-      <c r="C1702" s="1" t="inlineStr"/>
+      <c r="C1702" s="1" t="inlineStr">
+        <is>
+          <t>/maˈjoʁ/</t>
+        </is>
+      </c>
       <c r="D1702" s="1" t="inlineStr">
         <is>
-          <t>市长</t>
+          <t>（西班牙语词，非葡萄牙语）</t>
         </is>
       </c>
       <c r="E1702" s="1" t="inlineStr">
@@ -54936,7 +55032,7 @@
       </c>
       <c r="C1707" s="1" t="inlineStr">
         <is>
-          <t>ʃa.ˈma.ɾãʊ̃</t>
+          <t>/ʃa.ˈma.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D1707" s="1" t="inlineStr">
@@ -55123,7 +55219,7 @@
       </c>
       <c r="B1713" s="1" t="inlineStr">
         <is>
-          <t>[ˈmos.kɐ] 飞&lt;名&gt;</t>
+          <t>[ˈmos.kɐ] 苍蝇&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1713" s="1" t="inlineStr">
@@ -55133,7 +55229,7 @@
       </c>
       <c r="D1713" s="1" t="inlineStr">
         <is>
-          <t>飞</t>
+          <t>苍蝇</t>
         </is>
       </c>
       <c r="E1713" s="1" t="inlineStr">
@@ -55254,7 +55350,11 @@
           <t>博士&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C1717" s="1" t="inlineStr"/>
+      <c r="C1717" s="1" t="inlineStr">
+        <is>
+          <t>/do(w)ˈtoʁ/</t>
+        </is>
+      </c>
       <c r="D1717" s="1" t="inlineStr">
         <is>
           <t>博士</t>
@@ -55343,7 +55443,7 @@
       </c>
       <c r="B1720" s="1" t="inlineStr">
         <is>
-          <t>[ˈfa.ʃɐ] 轨道&lt;名&gt;</t>
+          <t>[ˈfa.ʃɐ] 带子；条纹；带；车道&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1720" s="1" t="inlineStr">
@@ -55353,7 +55453,7 @@
       </c>
       <c r="D1720" s="1" t="inlineStr">
         <is>
-          <t>轨道</t>
+          <t>带子；条纹；带；车道</t>
         </is>
       </c>
       <c r="E1720" s="1" t="inlineStr">
@@ -55378,7 +55478,11 @@
           <t>我们应该&lt;动&gt;</t>
         </is>
       </c>
-      <c r="C1721" s="1" t="inlineStr"/>
+      <c r="C1721" s="1" t="inlineStr">
+        <is>
+          <t>/de.ˈvi.a.mʊs/</t>
+        </is>
+      </c>
       <c r="D1721" s="1" t="inlineStr">
         <is>
           <t>我们应该</t>
@@ -55435,7 +55539,7 @@
       </c>
       <c r="B1723" s="1" t="inlineStr">
         <is>
-          <t>[ˈkuw.tu] 邪教&lt;名&gt;</t>
+          <t>[ˈkuw.tu] 礼拜；崇拜&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1723" s="1" t="inlineStr">
@@ -55445,7 +55549,7 @@
       </c>
       <c r="D1723" s="1" t="inlineStr">
         <is>
-          <t>邪教</t>
+          <t>礼拜；崇拜</t>
         </is>
       </c>
       <c r="E1723" s="1" t="inlineStr">
@@ -55568,7 +55672,7 @@
       </c>
       <c r="C1727" s="1" t="inlineStr">
         <is>
-          <t>ĩ.ʒe.ˈsãʊ̃</t>
+          <t>/ĩ.ʒe.ˈsãʊ̃/</t>
         </is>
       </c>
       <c r="D1727" s="1" t="inlineStr">
@@ -55979,7 +56083,7 @@
       </c>
       <c r="B1740" s="1" t="inlineStr">
         <is>
-          <t>[(i)ʃ.tɐ.sjuˈnaɾ] 公园&lt;动&gt;</t>
+          <t>[(i)ʃ.tɐ.sjuˈnaɾ] 停车；停放（车辆）&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1740" s="1" t="inlineStr">
@@ -55989,7 +56093,7 @@
       </c>
       <c r="D1740" s="1" t="inlineStr">
         <is>
-          <t>公园</t>
+          <t>停车；停放（车辆）</t>
         </is>
       </c>
       <c r="E1740" s="1" t="inlineStr">
@@ -56331,7 +56435,7 @@
       </c>
       <c r="B1751" s="1" t="inlineStr">
         <is>
-          <t>[fawˈkɐ̃w̃] 鹰&lt;名&gt;</t>
+          <t>[/fawˈkɐ̃w̃/] 隼；猎鹰&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1751" s="1" t="inlineStr">
@@ -56341,7 +56445,7 @@
       </c>
       <c r="D1751" s="1" t="inlineStr">
         <is>
-          <t>鹰</t>
+          <t>隼；猎鹰&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1751" s="1" t="inlineStr">
@@ -56907,7 +57011,7 @@
       </c>
       <c r="B1769" s="1" t="inlineStr">
         <is>
-          <t>[noˈta(ʁ)] 通知&lt;动&gt;</t>
+          <t>[noˈta(ʁ)] 注意到；察觉&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1769" s="1" t="inlineStr">
@@ -56917,7 +57021,7 @@
       </c>
       <c r="D1769" s="1" t="inlineStr">
         <is>
-          <t>通知</t>
+          <t>注意到；察觉</t>
         </is>
       </c>
       <c r="E1769" s="1" t="inlineStr">
@@ -56939,7 +57043,7 @@
       </c>
       <c r="B1770" s="1" t="inlineStr">
         <is>
-          <t>[pasˈt͡ʃi.ʎɐ] 平板电脑&lt;名&gt;</t>
+          <t>[pasˈt͡ʃi.ʎɐ] 药片；含片；小圆片；刹车片&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1770" s="1" t="inlineStr">
@@ -56949,7 +57053,7 @@
       </c>
       <c r="D1770" s="1" t="inlineStr">
         <is>
-          <t>平板电脑</t>
+          <t>药片；含片；小圆片；刹车片</t>
         </is>
       </c>
       <c r="E1770" s="1" t="inlineStr">
@@ -57931,7 +58035,7 @@
       </c>
       <c r="B1801" s="1" t="inlineStr">
         <is>
-          <t>[viˈvi.du] 住过&lt;形&gt;</t>
+          <t>[viˈvi.du] 经历过的；生活过的&lt;形&gt;</t>
         </is>
       </c>
       <c r="C1801" s="1" t="inlineStr">
@@ -57941,7 +58045,7 @@
       </c>
       <c r="D1801" s="1" t="inlineStr">
         <is>
-          <t>住过</t>
+          <t>经历过的；生活过的</t>
         </is>
       </c>
       <c r="E1801" s="1" t="inlineStr">
@@ -57963,7 +58067,7 @@
       </c>
       <c r="B1802" s="1" t="inlineStr">
         <is>
-          <t>[kɾuˈza(ʁ)] 十字&lt;动&gt;</t>
+          <t>[kɾuˈza(ʁ)] 穿过；交叉；横渡；杂交&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1802" s="1" t="inlineStr">
@@ -57973,7 +58077,7 @@
       </c>
       <c r="D1802" s="1" t="inlineStr">
         <is>
-          <t>十字</t>
+          <t>穿过；交叉；横渡；杂交</t>
         </is>
       </c>
       <c r="E1802" s="1" t="inlineStr">
@@ -58192,7 +58296,7 @@
       </c>
       <c r="C1809" s="1" t="inlineStr">
         <is>
-          <t>i.ˈɾis</t>
+          <t>/i.ˈɾis/</t>
         </is>
       </c>
       <c r="D1809" s="1" t="inlineStr">
@@ -58320,7 +58424,7 @@
       </c>
       <c r="C1813" s="1" t="inlineStr">
         <is>
-          <t>ko.xe.ta.ˈmẽ.tʃɪ</t>
+          <t>/ko.xe.ta.ˈmẽ.tʃɪ/</t>
         </is>
       </c>
       <c r="D1813" s="1" t="inlineStr">
@@ -58608,7 +58712,7 @@
       </c>
       <c r="C1822" s="1" t="inlineStr">
         <is>
-          <t>a.tu.a.ˈsãʊ̃</t>
+          <t>/a.tu.a.ˈsãʊ̃/</t>
         </is>
       </c>
       <c r="D1822" s="1" t="inlineStr">
@@ -59147,17 +59251,17 @@
       </c>
       <c r="B1839" s="1" t="inlineStr">
         <is>
-          <t>[a.ta.ˈka.ɾãʊ̃] 受到攻击&lt;动&gt;</t>
+          <t>[a.ta.ˈka.ɾãʊ̃] 攻击；袭击&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1839" s="1" t="inlineStr">
         <is>
-          <t>a.ta.ˈka.ɾãʊ̃</t>
+          <t>/a.ta.ˈka.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D1839" s="1" t="inlineStr">
         <is>
-          <t>受到攻击</t>
+          <t>攻击；袭击</t>
         </is>
       </c>
       <c r="E1839" s="1" t="inlineStr">
@@ -59246,7 +59350,11 @@
           <t>毫米&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C1842" s="1" t="inlineStr"/>
+      <c r="C1842" s="1" t="inlineStr">
+        <is>
+          <t>/miˈlĩ.me.tɾu/</t>
+        </is>
+      </c>
       <c r="D1842" s="1" t="inlineStr">
         <is>
           <t>毫米</t>
@@ -59303,7 +59411,7 @@
       </c>
       <c r="B1844" s="1" t="inlineStr">
         <is>
-          <t>[ˈtaʁ.du] 迟到了&lt;形&gt;</t>
+          <t>[/ˈtaʁ.du/] 迟的；迟缓的（标准形为 tardio）&lt;形&gt;&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C1844" s="1" t="inlineStr">
@@ -59313,7 +59421,7 @@
       </c>
       <c r="D1844" s="1" t="inlineStr">
         <is>
-          <t>迟到了</t>
+          <t>迟的；迟缓的（标准形为 tardio）&lt;形&gt;</t>
         </is>
       </c>
       <c r="E1844" s="1" t="inlineStr">
@@ -59591,7 +59699,7 @@
       </c>
       <c r="B1853" s="1" t="inlineStr">
         <is>
-          <t>[a.ʁaˈza(ʁ)] 暗恋&lt;动&gt;</t>
+          <t>[a.ʁaˈza(ʁ)] 摧毁；夷平；毁坏&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1853" s="1" t="inlineStr">
@@ -59601,7 +59709,7 @@
       </c>
       <c r="D1853" s="1" t="inlineStr">
         <is>
-          <t>暗恋</t>
+          <t>摧毁；夷平；毁坏</t>
         </is>
       </c>
       <c r="E1853" s="1" t="inlineStr">
@@ -59687,7 +59795,7 @@
       </c>
       <c r="B1856" s="1" t="inlineStr">
         <is>
-          <t>[a.t͡ʃiˈɾa.du] 抛出&lt;形&gt;</t>
+          <t>[/a.t͡ʃiˈɾa.du/] 投掷的；被抛出的&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C1856" s="1" t="inlineStr">
@@ -59697,7 +59805,7 @@
       </c>
       <c r="D1856" s="1" t="inlineStr">
         <is>
-          <t>抛出</t>
+          <t>投掷的；被抛出的</t>
         </is>
       </c>
       <c r="E1856" s="1" t="inlineStr">
@@ -59783,7 +59891,7 @@
       </c>
       <c r="B1859" s="1" t="inlineStr">
         <is>
-          <t>[kɾisˈtɐ̃w̃] 基督教&lt;名&gt;</t>
+          <t>[kɾisˈtɐ̃w̃] 基督徒；基督教的&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1859" s="1" t="inlineStr">
@@ -59793,7 +59901,7 @@
       </c>
       <c r="D1859" s="1" t="inlineStr">
         <is>
-          <t>基督教</t>
+          <t>基督徒；基督教的</t>
         </is>
       </c>
       <c r="E1859" s="1" t="inlineStr">
@@ -59943,7 +60051,7 @@
       </c>
       <c r="B1864" s="1" t="inlineStr">
         <is>
-          <t>[maˈnɔ.bɾɐ] 演习&lt;名&gt;</t>
+          <t>[/maˈnɔ.bɾɐ/] 操作；机动；策略（复数可指军事演习）&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1864" s="1" t="inlineStr">
@@ -59953,7 +60061,7 @@
       </c>
       <c r="D1864" s="1" t="inlineStr">
         <is>
-          <t>演习</t>
+          <t>操作；机动；策略（复数可指军事演习）</t>
         </is>
       </c>
       <c r="E1864" s="1" t="inlineStr">
@@ -60103,17 +60211,17 @@
       </c>
       <c r="B1869" s="1" t="inlineStr">
         <is>
-          <t>[li.ˈga.ɾãʊ̃] 被称为&lt;动&gt;</t>
+          <t>[li.ˈga.ɾãʊ̃] 打电话；连接；打开&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1869" s="1" t="inlineStr">
         <is>
-          <t>li.ˈga.ɾãʊ̃</t>
+          <t>/li.ˈga.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D1869" s="1" t="inlineStr">
         <is>
-          <t>被称为</t>
+          <t>打电话；连接；打开</t>
         </is>
       </c>
       <c r="E1869" s="1" t="inlineStr">
@@ -60807,7 +60915,7 @@
       </c>
       <c r="B1891" s="1" t="inlineStr">
         <is>
-          <t>[de.miˈsɐ̃w̃] 解雇&lt;名&gt;</t>
+          <t>[/de.miˈsɐ̃w̃/] 辞职；解职&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1891" s="1" t="inlineStr">
@@ -60817,7 +60925,7 @@
       </c>
       <c r="D1891" s="1" t="inlineStr">
         <is>
-          <t>解雇</t>
+          <t>辞职；解职&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1891" s="1" t="inlineStr">
@@ -60938,10 +61046,14 @@
           <t>灰色&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C1895" s="1" t="inlineStr"/>
+      <c r="C1895" s="1" t="inlineStr">
+        <is>
+          <t>/ɡɹeɪ/</t>
+        </is>
+      </c>
       <c r="D1895" s="1" t="inlineStr">
         <is>
-          <t>灰色</t>
+          <t>非葡萄牙语词；葡萄牙语为 cinza 灰色&lt;名&gt;</t>
         </is>
       </c>
       <c r="E1895" s="1" t="inlineStr">
@@ -61187,17 +61299,17 @@
       </c>
       <c r="B1903" s="1" t="inlineStr">
         <is>
-          <t>[ˈa.və] 艾娃&lt;叹&gt;</t>
+          <t>[ˈa.və] 哎呀（表示惊讶或愤怒的感叹声）&lt;叹&gt;</t>
         </is>
       </c>
       <c r="C1903" s="1" t="inlineStr">
         <is>
-          <t>ˈa.və</t>
+          <t>/ˈa.və/</t>
         </is>
       </c>
       <c r="D1903" s="1" t="inlineStr">
         <is>
-          <t>艾娃</t>
+          <t>哎呀（表示惊讶或愤怒的感叹声）</t>
         </is>
       </c>
       <c r="E1903" s="1" t="inlineStr">
@@ -61443,7 +61555,7 @@
       </c>
       <c r="B1911" s="1" t="inlineStr">
         <is>
-          <t>[ko.ʁes.põˈde(ʁ)] 比赛&lt;动&gt;</t>
+          <t>[ko.ʁes.põˈde(ʁ)] 符合；相当于；对应；回应&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1911" s="1" t="inlineStr">
@@ -61453,7 +61565,7 @@
       </c>
       <c r="D1911" s="1" t="inlineStr">
         <is>
-          <t>比赛</t>
+          <t>符合；相当于；对应；回应</t>
         </is>
       </c>
       <c r="E1911" s="1" t="inlineStr">
@@ -61539,7 +61651,7 @@
       </c>
       <c r="B1914" s="1" t="inlineStr">
         <is>
-          <t>[kũˈɲa.du] 妹夫&lt;名&gt;</t>
+          <t>[/kũˈɲa.du/] 姐夫；妹夫；内兄；连襟（配偶的兄弟或姐妹的丈夫）&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C1914" s="1" t="inlineStr">
@@ -61549,7 +61661,7 @@
       </c>
       <c r="D1914" s="1" t="inlineStr">
         <is>
-          <t>妹夫</t>
+          <t>姐夫；妹夫；内兄；连襟（配偶的兄弟或姐妹的丈夫）</t>
         </is>
       </c>
       <c r="E1914" s="1" t="inlineStr">
@@ -61603,17 +61715,17 @@
       </c>
       <c r="B1916" s="1" t="inlineStr">
         <is>
-          <t>[pax.ˈtʃi.ɾãʊ̃] 左&lt;动&gt;</t>
+          <t>[pax.ˈtʃi.ɾãʊ̃] 离开；出发&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1916" s="1" t="inlineStr">
         <is>
-          <t>pax.ˈtʃi.ɾãʊ̃</t>
+          <t>/pax.ˈtʃi.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D1916" s="1" t="inlineStr">
         <is>
-          <t>左</t>
+          <t>离开；出发</t>
         </is>
       </c>
       <c r="E1916" s="1" t="inlineStr">
@@ -61702,7 +61814,11 @@
           <t>夫人&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C1919" s="1" t="inlineStr"/>
+      <c r="C1919" s="1" t="inlineStr">
+        <is>
+          <t>/sẽˈɲɔ.ɾɐ/</t>
+        </is>
+      </c>
       <c r="D1919" s="1" t="inlineStr">
         <is>
           <t>夫人</t>
@@ -61860,7 +61976,7 @@
       </c>
       <c r="C1924" s="1" t="inlineStr">
         <is>
-          <t>a.fe.ˈtax</t>
+          <t>/a.fe.ˈtax/</t>
         </is>
       </c>
       <c r="D1924" s="1" t="inlineStr">
@@ -62628,7 +62744,7 @@
       </c>
       <c r="C1948" s="1" t="inlineStr">
         <is>
-          <t>dʒis.tɾa.ˈsãʊ̃</t>
+          <t>/dʒis.tɾa.ˈsãʊ̃/</t>
         </is>
       </c>
       <c r="D1948" s="1" t="inlineStr">
@@ -62719,7 +62835,7 @@
       </c>
       <c r="B1951" s="1" t="inlineStr">
         <is>
-          <t>[zoˈna(ʁ)] 区&lt;动&gt;</t>
+          <t>[zoˈna(ʁ)] 划分区域；分区&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1951" s="1" t="inlineStr">
@@ -62729,7 +62845,7 @@
       </c>
       <c r="D1951" s="1" t="inlineStr">
         <is>
-          <t>区</t>
+          <t>划分区域；分区</t>
         </is>
       </c>
       <c r="E1951" s="1" t="inlineStr">
@@ -63135,7 +63251,7 @@
       </c>
       <c r="B1964" s="1" t="inlineStr">
         <is>
-          <t>[ʁeˈflɛk.su] 反思&lt;名&gt;</t>
+          <t>[ʁeˈflɛk.su] 反射；映像；倒影；反射作用&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1964" s="1" t="inlineStr">
@@ -63145,7 +63261,7 @@
       </c>
       <c r="D1964" s="1" t="inlineStr">
         <is>
-          <t>反思</t>
+          <t>反射；映像；倒影；反射作用</t>
         </is>
       </c>
       <c r="E1964" s="1" t="inlineStr">
@@ -63263,7 +63379,7 @@
       </c>
       <c r="B1968" s="1" t="inlineStr">
         <is>
-          <t>[ˈkɛ.kɐ] 他妈的&lt;名&gt;</t>
+          <t>[ˈkɛ.kɐ] 性交&lt;名&gt;</t>
         </is>
       </c>
       <c r="C1968" s="1" t="inlineStr">
@@ -63273,7 +63389,7 @@
       </c>
       <c r="D1968" s="1" t="inlineStr">
         <is>
-          <t>他妈的</t>
+          <t>性交</t>
         </is>
       </c>
       <c r="E1968" s="1" t="inlineStr">
@@ -63364,7 +63480,7 @@
       </c>
       <c r="C1971" s="1" t="inlineStr">
         <is>
-          <t>xe.se.ˈbe.ɾãʊ̃</t>
+          <t>/xe.se.ˈbe.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D1971" s="1" t="inlineStr">
@@ -63999,7 +64115,7 @@
       </c>
       <c r="B1991" s="1" t="inlineStr">
         <is>
-          <t>[õˈʁa(ʁ)] 荣誉&lt;动&gt;</t>
+          <t>[õˈʁa(ʁ)] 尊敬；致敬；履行&lt;动&gt;</t>
         </is>
       </c>
       <c r="C1991" s="1" t="inlineStr">
@@ -64009,7 +64125,7 @@
       </c>
       <c r="D1991" s="1" t="inlineStr">
         <is>
-          <t>荣誉</t>
+          <t>尊敬；致敬；履行</t>
         </is>
       </c>
       <c r="E1991" s="1" t="inlineStr">
@@ -64482,7 +64598,11 @@
           <t>判决&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C2006" s="1" t="inlineStr"/>
+      <c r="C2006" s="1" t="inlineStr">
+        <is>
+          <t>/ve.ɾeˈdik.tu/</t>
+        </is>
+      </c>
       <c r="D2006" s="1" t="inlineStr">
         <is>
           <t>判决</t>
@@ -64571,13 +64691,17 @@
       </c>
       <c r="B2009" s="1" t="inlineStr">
         <is>
-          <t>条带&lt;名&gt;</t>
-        </is>
-      </c>
-      <c r="C2009" s="1" t="inlineStr"/>
+          <t>[[stɹɪp]] 脱衣舞（strip-tease）&lt;noun&gt;</t>
+        </is>
+      </c>
+      <c r="C2009" s="1" t="inlineStr">
+        <is>
+          <t>/isˈtɾi.pi/</t>
+        </is>
+      </c>
       <c r="D2009" s="1" t="inlineStr">
         <is>
-          <t>条带</t>
+          <t>脱衣舞（strip-tease）</t>
         </is>
       </c>
       <c r="E2009" s="1" t="inlineStr">
@@ -64663,7 +64787,7 @@
       </c>
       <c r="B2012" s="1" t="inlineStr">
         <is>
-          <t>[ko.loˈɾa.du] 科罗拉多州&lt;名&gt;</t>
+          <t>[ko.loˈɾa.du] 红色的；红润的&lt;名&gt;</t>
         </is>
       </c>
       <c r="C2012" s="1" t="inlineStr">
@@ -64673,7 +64797,7 @@
       </c>
       <c r="D2012" s="1" t="inlineStr">
         <is>
-          <t>科罗拉多州</t>
+          <t>红色的；红润的</t>
         </is>
       </c>
       <c r="E2012" s="1" t="inlineStr">
@@ -65015,7 +65139,7 @@
       </c>
       <c r="B2023" s="1" t="inlineStr">
         <is>
-          <t>[miˈmi(ʁ)] 宠爱&lt;动&gt;</t>
+          <t>[/miˈmi(ʁ)/] 睡觉（儿语）&lt;动&gt;&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C2023" s="1" t="inlineStr">
@@ -65025,7 +65149,7 @@
       </c>
       <c r="D2023" s="1" t="inlineStr">
         <is>
-          <t>宠爱</t>
+          <t>睡觉（儿语）&lt;动&gt;</t>
         </is>
       </c>
       <c r="E2023" s="1" t="inlineStr">
@@ -65047,7 +65171,7 @@
       </c>
       <c r="B2024" s="1" t="inlineStr">
         <is>
-          <t>[kõ.d͡ʒi.si.oˈna.du] 调理&lt;形&gt;</t>
+          <t>[kõ.d͡ʒi.si.oˈna.du] 受制约的；有条件的；装有空调的&lt;形&gt;</t>
         </is>
       </c>
       <c r="C2024" s="1" t="inlineStr">
@@ -65057,7 +65181,7 @@
       </c>
       <c r="D2024" s="1" t="inlineStr">
         <is>
-          <t>调理</t>
+          <t>受制约的；有条件的；装有空调的</t>
         </is>
       </c>
       <c r="E2024" s="1" t="inlineStr">
@@ -65079,13 +65203,17 @@
       </c>
       <c r="B2025" s="1" t="inlineStr">
         <is>
-          <t>是吗&lt;动&gt;</t>
-        </is>
-      </c>
-      <c r="C2025" s="1" t="inlineStr"/>
+          <t>[[ɨʃˈta]] está 在；处于&lt;动&gt;&lt;verb&gt;</t>
+        </is>
+      </c>
+      <c r="C2025" s="1" t="inlineStr">
+        <is>
+          <t>/is.ˈta(ʁ)/</t>
+        </is>
+      </c>
       <c r="D2025" s="1" t="inlineStr">
         <is>
-          <t>是吗</t>
+          <t>está 在；处于&lt;动&gt;</t>
         </is>
       </c>
       <c r="E2025" s="1" t="inlineStr">
@@ -65747,7 +65875,7 @@
       </c>
       <c r="B2046" s="1" t="inlineStr">
         <is>
-          <t>[sĩ.paˈt͡ʃi.ɐ] 同情&lt;名&gt;</t>
+          <t>[/sĩ.paˈt͡ʃi.ɐ/] 好感；和蔼可亲&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2046" s="1" t="inlineStr">
@@ -65757,7 +65885,7 @@
       </c>
       <c r="D2046" s="1" t="inlineStr">
         <is>
-          <t>同情</t>
+          <t>好感；和蔼可亲&lt;名&gt;</t>
         </is>
       </c>
       <c r="E2046" s="1" t="inlineStr">
@@ -65848,7 +65976,7 @@
       </c>
       <c r="C2049" s="1" t="inlineStr">
         <is>
-          <t>ˈta.tʃi.kə</t>
+          <t>/ˈta.tʃi.kə/</t>
         </is>
       </c>
       <c r="D2049" s="1" t="inlineStr">
@@ -66136,7 +66264,7 @@
       </c>
       <c r="C2058" s="1" t="inlineStr">
         <is>
-          <t>pa.ɾa.ˈnɔy.kʊ</t>
+          <t>/pa.ɾa.ˈnɔy.kʊ/</t>
         </is>
       </c>
       <c r="D2058" s="1" t="inlineStr">
@@ -66584,7 +66712,7 @@
       </c>
       <c r="C2072" s="1" t="inlineStr">
         <is>
-          <t>fuˈlɐ̃.nu</t>
+          <t>/fuˈlɐ̃.nu/</t>
         </is>
       </c>
       <c r="D2072" s="1" t="inlineStr">
@@ -66803,7 +66931,7 @@
       </c>
       <c r="B2079" s="1" t="inlineStr">
         <is>
-          <t>[ɡaˈba(ʁ)] 吹牛&lt;动&gt;</t>
+          <t>[/ɡaˈba(ʁ)/] 称赞；夸奖（gabar-se de 为自夸）&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C2079" s="1" t="inlineStr">
@@ -66813,7 +66941,7 @@
       </c>
       <c r="D2079" s="1" t="inlineStr">
         <is>
-          <t>吹牛</t>
+          <t>称赞；夸奖（gabar-se de 为自夸）</t>
         </is>
       </c>
       <c r="E2079" s="1" t="inlineStr">
@@ -66840,7 +66968,7 @@
       </c>
       <c r="C2080" s="1" t="inlineStr">
         <is>
-          <t>kɾi.ˈa.ɾãʊ̃</t>
+          <t>/kɾi.ˈa.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D2080" s="1" t="inlineStr">
@@ -67315,17 +67443,17 @@
       </c>
       <c r="B2095" s="1" t="inlineStr">
         <is>
-          <t>[es.ta.ˈvã.mʊs] 我们是&lt;动&gt;</t>
+          <t>[es.ta.ˈvã.mʊs] estávamos：我们是/我们在（estar的陈述式过去未完成时第一人称复数）&lt;动&gt;&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C2095" s="1" t="inlineStr">
         <is>
-          <t>es.ta.ˈvã.mʊs</t>
+          <t>/es.ta.ˈvã.mʊs/</t>
         </is>
       </c>
       <c r="D2095" s="1" t="inlineStr">
         <is>
-          <t>我们是</t>
+          <t>estávamos：我们是/我们在（estar的陈述式过去未完成时第一人称复数）&lt;动&gt;</t>
         </is>
       </c>
       <c r="E2095" s="1" t="inlineStr">
@@ -67382,7 +67510,11 @@
           <t>阿尔法&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C2097" s="1" t="inlineStr"/>
+      <c r="C2097" s="1" t="inlineStr">
+        <is>
+          <t>/ˈal.fɐ/</t>
+        </is>
+      </c>
       <c r="D2097" s="1" t="inlineStr">
         <is>
           <t>阿尔法</t>
@@ -67538,7 +67670,11 @@
           <t>屁股&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C2102" s="1" t="inlineStr"/>
+      <c r="C2102" s="1" t="inlineStr">
+        <is>
+          <t>/ˈku/</t>
+        </is>
+      </c>
       <c r="D2102" s="1" t="inlineStr">
         <is>
           <t>屁股</t>
@@ -67691,7 +67827,7 @@
       </c>
       <c r="B2107" s="1" t="inlineStr">
         <is>
-          <t>[po(w)ˈza(ʁ)] 土地&lt;动&gt;</t>
+          <t>[po(w)ˈza(ʁ)] 降落；栖息；放下&lt;动&gt;</t>
         </is>
       </c>
       <c r="C2107" s="1" t="inlineStr">
@@ -67701,7 +67837,7 @@
       </c>
       <c r="D2107" s="1" t="inlineStr">
         <is>
-          <t>土地</t>
+          <t>降落；栖息；放下</t>
         </is>
       </c>
       <c r="E2107" s="1" t="inlineStr">
@@ -67723,7 +67859,7 @@
       </c>
       <c r="B2108" s="1" t="inlineStr">
         <is>
-          <t>[ˈpɔ.pi] 教皇&lt;名&gt;</t>
+          <t>[/ˈpɔ.pi/] 教皇&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2108" s="1" t="inlineStr">
@@ -67947,7 +68083,7 @@
       </c>
       <c r="B2115" s="1" t="inlineStr">
         <is>
-          <t>[aˈba(ʁ)] 打开&lt;动&gt;</t>
+          <t>[/aˈba(ʁ)/] 打开&lt;verb&gt;</t>
         </is>
       </c>
       <c r="C2115" s="1" t="inlineStr">
@@ -68080,7 +68216,7 @@
       </c>
       <c r="C2119" s="1" t="inlineStr">
         <is>
-          <t>a.dop.ˈsãʊ̃</t>
+          <t>/a.dop.ˈsãʊ̃/</t>
         </is>
       </c>
       <c r="D2119" s="1" t="inlineStr">
@@ -68235,17 +68371,17 @@
       </c>
       <c r="B2124" s="1" t="inlineStr">
         <is>
-          <t>[i.ni.ˈsi.ʊ] 家&lt;名&gt;</t>
+          <t>[i.ni.ˈsi.ʊ] 开始；开端&lt;名&gt;</t>
         </is>
       </c>
       <c r="C2124" s="1" t="inlineStr">
         <is>
-          <t>i.ni.ˈsi.ʊ</t>
+          <t>/i.ni.ˈsi.ʊ/</t>
         </is>
       </c>
       <c r="D2124" s="1" t="inlineStr">
         <is>
-          <t>家</t>
+          <t>开始；开端</t>
         </is>
       </c>
       <c r="E2124" s="1" t="inlineStr">
@@ -68395,7 +68531,7 @@
       </c>
       <c r="B2129" s="1" t="inlineStr">
         <is>
-          <t>[ˈvaw] 瓦尔&lt;名&gt;</t>
+          <t>[/ˈvaw/] 山谷&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2129" s="1" t="inlineStr">
@@ -68405,7 +68541,7 @@
       </c>
       <c r="D2129" s="1" t="inlineStr">
         <is>
-          <t>瓦尔</t>
+          <t>山谷&lt;名&gt;</t>
         </is>
       </c>
       <c r="E2129" s="1" t="inlineStr">
@@ -68558,7 +68694,11 @@
           <t>喷射机&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C2134" s="1" t="inlineStr"/>
+      <c r="C2134" s="1" t="inlineStr">
+        <is>
+          <t>/ˈʒak.tu/</t>
+        </is>
+      </c>
       <c r="D2134" s="1" t="inlineStr">
         <is>
           <t>喷射机</t>
@@ -68583,17 +68723,17 @@
       </c>
       <c r="B2135" s="1" t="inlineStr">
         <is>
-          <t>[ˈtɾɔ.kʊs] 改变&lt;名&gt;</t>
+          <t>[ˈtɾɔ.kʊs] 找零；零钱&lt;名&gt;</t>
         </is>
       </c>
       <c r="C2135" s="1" t="inlineStr">
         <is>
-          <t>ˈtɾɔ.kʊs</t>
+          <t>/ˈtɾɔ.kʊs/</t>
         </is>
       </c>
       <c r="D2135" s="1" t="inlineStr">
         <is>
-          <t>改变</t>
+          <t>找零；零钱</t>
         </is>
       </c>
       <c r="E2135" s="1" t="inlineStr">
@@ -68716,7 +68856,7 @@
       </c>
       <c r="C2139" s="1" t="inlineStr">
         <is>
-          <t>ẽ.vi.ˈa.ɾãʊ̃</t>
+          <t>/ẽ.vi.ˈa.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D2139" s="1" t="inlineStr">
@@ -68999,7 +69139,7 @@
       </c>
       <c r="B2148" s="1" t="inlineStr">
         <is>
-          <t>[saˈbi.du] 已知的&lt;形&gt;</t>
+          <t>[/saˈbi.du/] 知道的&lt;形&gt;；有见识的&lt;形&gt;&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C2148" s="1" t="inlineStr">
@@ -69009,7 +69149,7 @@
       </c>
       <c r="D2148" s="1" t="inlineStr">
         <is>
-          <t>已知的</t>
+          <t>知道的&lt;形&gt;；有见识的&lt;形&gt;</t>
         </is>
       </c>
       <c r="E2148" s="1" t="inlineStr">
@@ -69031,7 +69171,7 @@
       </c>
       <c r="B2149" s="1" t="inlineStr">
         <is>
-          <t>[kɾuˈze(j).ɾu] 巡航&lt;名&gt;</t>
+          <t>[/kɾuˈze(j).ɾu/] 十字&lt;名&gt;；南十字座&lt;名&gt;；克鲁塞罗（巴西旧货币）&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2149" s="1" t="inlineStr">
@@ -69041,7 +69181,7 @@
       </c>
       <c r="D2149" s="1" t="inlineStr">
         <is>
-          <t>巡航</t>
+          <t>十字&lt;名&gt;；南十字座&lt;名&gt;；克鲁塞罗（巴西旧货币）&lt;名&gt;</t>
         </is>
       </c>
       <c r="E2149" s="1" t="inlineStr">
@@ -69258,7 +69398,11 @@
           <t>不&lt;叹&gt;</t>
         </is>
       </c>
-      <c r="C2156" s="1" t="inlineStr"/>
+      <c r="C2156" s="1" t="inlineStr">
+        <is>
+          <t>/nɐ̃w̃/</t>
+        </is>
+      </c>
       <c r="D2156" s="1" t="inlineStr">
         <is>
           <t>不</t>
@@ -69315,7 +69459,7 @@
       </c>
       <c r="B2158" s="1" t="inlineStr">
         <is>
-          <t>[is.pɾeˈsa(ʁ)] 快递&lt;动&gt;</t>
+          <t>[is.pɾeˈsa(ʁ)] 表达；表示&lt;动&gt;</t>
         </is>
       </c>
       <c r="C2158" s="1" t="inlineStr">
@@ -69325,7 +69469,7 @@
       </c>
       <c r="D2158" s="1" t="inlineStr">
         <is>
-          <t>快递</t>
+          <t>表达；表示</t>
         </is>
       </c>
       <c r="E2158" s="1" t="inlineStr">
@@ -69384,7 +69528,7 @@
       </c>
       <c r="C2160" s="1" t="inlineStr">
         <is>
-          <t>ˈnĩ.gẽỹ</t>
+          <t>/ˈnĩ.gẽỹ/</t>
         </is>
       </c>
       <c r="D2160" s="1" t="inlineStr">
@@ -69443,7 +69587,7 @@
       </c>
       <c r="B2162" s="1" t="inlineStr">
         <is>
-          <t>[ˈli.dɐ] 读&lt;名&gt;</t>
+          <t>[ˈli.dɐ] 农活；劳作&lt;名&gt;</t>
         </is>
       </c>
       <c r="C2162" s="1" t="inlineStr">
@@ -69453,7 +69597,7 @@
       </c>
       <c r="D2162" s="1" t="inlineStr">
         <is>
-          <t>读</t>
+          <t>农活；劳作</t>
         </is>
       </c>
       <c r="E2162" s="1" t="inlineStr">
@@ -69512,7 +69656,7 @@
       </c>
       <c r="C2164" s="1" t="inlineStr">
         <is>
-          <t>fɾa.ˈtu.ɾə</t>
+          <t>/fɾa.ˈtu.ɾə/</t>
         </is>
       </c>
       <c r="D2164" s="1" t="inlineStr">
@@ -69603,7 +69747,7 @@
       </c>
       <c r="B2167" s="1" t="inlineStr">
         <is>
-          <t>[d͡ʒi.ɡɾeˈsɐ̃w̃] 游览&lt;名&gt;</t>
+          <t>[/d͡ʒi.ɡɾeˈsɐ̃w̃/] 离题&lt;名&gt;；枝蔓&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2167" s="1" t="inlineStr">
@@ -69613,7 +69757,7 @@
       </c>
       <c r="D2167" s="1" t="inlineStr">
         <is>
-          <t>游览</t>
+          <t>离题&lt;名&gt;；枝蔓&lt;名&gt;</t>
         </is>
       </c>
       <c r="E2167" s="1" t="inlineStr">
@@ -69736,7 +69880,7 @@
       </c>
       <c r="C2171" s="1" t="inlineStr">
         <is>
-          <t>po.si.ˈvew</t>
+          <t>/po.si.ˈvew/</t>
         </is>
       </c>
       <c r="D2171" s="1" t="inlineStr">
@@ -70051,7 +70195,7 @@
       </c>
       <c r="B2181" s="1" t="inlineStr">
         <is>
-          <t>[ˈlɔ.t͡ʃi] 很多&lt;名&gt;</t>
+          <t>[ˈlɔ.t͡ʃi] 地块；一批；份额&lt;名&gt;</t>
         </is>
       </c>
       <c r="C2181" s="1" t="inlineStr">
@@ -70061,7 +70205,7 @@
       </c>
       <c r="D2181" s="1" t="inlineStr">
         <is>
-          <t>很多</t>
+          <t>地块；一批；份额</t>
         </is>
       </c>
       <c r="E2181" s="1" t="inlineStr">
@@ -70088,7 +70232,7 @@
       </c>
       <c r="C2182" s="1" t="inlineStr">
         <is>
-          <t>gã.ˈɲa.ɾãʊ̃</t>
+          <t>/gã.ˈɲa.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D2182" s="1" t="inlineStr">
@@ -70248,7 +70392,7 @@
       </c>
       <c r="C2187" s="1" t="inlineStr">
         <is>
-          <t>ˈpe.lʊ</t>
+          <t>/ˈpe.lʊ/</t>
         </is>
       </c>
       <c r="D2187" s="1" t="inlineStr">
@@ -70275,17 +70419,17 @@
       </c>
       <c r="B2188" s="1" t="inlineStr">
         <is>
-          <t>[nu.ˈmɛ.ɾʊ] 数量&lt;名&gt;</t>
+          <t>[nu.ˈmɛ.ɾʊ] 数字&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2188" s="1" t="inlineStr">
         <is>
-          <t>nu.ˈmɛ.ɾʊ</t>
+          <t>/nu.ˈmɛ.ɾʊ/</t>
         </is>
       </c>
       <c r="D2188" s="1" t="inlineStr">
         <is>
-          <t>数量</t>
+          <t>数字&lt;名&gt;</t>
         </is>
       </c>
       <c r="E2188" s="1" t="inlineStr">
@@ -70883,7 +71027,7 @@
       </c>
       <c r="B2207" s="1" t="inlineStr">
         <is>
-          <t>[ˈsɔ.vɐ] 揉&lt;名&gt;</t>
+          <t>[/ˈsɔ.vɐ/] 毒打；痛打&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2207" s="1" t="inlineStr">
@@ -70893,7 +71037,7 @@
       </c>
       <c r="D2207" s="1" t="inlineStr">
         <is>
-          <t>揉</t>
+          <t>毒打；痛打&lt;名&gt;</t>
         </is>
       </c>
       <c r="E2207" s="1" t="inlineStr">
@@ -71011,7 +71155,7 @@
       </c>
       <c r="B2211" s="1" t="inlineStr">
         <is>
-          <t>[ʁe.koˈʁe(ʁ)] 度假村&lt;动&gt;</t>
+          <t>[ʁe.koˈʁe(ʁ)] 求助；诉诸；上诉&lt;动&gt;</t>
         </is>
       </c>
       <c r="C2211" s="1" t="inlineStr">
@@ -71021,7 +71165,7 @@
       </c>
       <c r="D2211" s="1" t="inlineStr">
         <is>
-          <t>度假村</t>
+          <t>求助；诉诸；上诉</t>
         </is>
       </c>
       <c r="E2211" s="1" t="inlineStr">
@@ -71139,7 +71283,7 @@
       </c>
       <c r="B2215" s="1" t="inlineStr">
         <is>
-          <t>[dez.majˈa(ʁ)] 微弱的&lt;动&gt;</t>
+          <t>[dez.majˈa(ʁ)] 昏倒；晕厥；褪色&lt;动&gt;</t>
         </is>
       </c>
       <c r="C2215" s="1" t="inlineStr">
@@ -71149,7 +71293,7 @@
       </c>
       <c r="D2215" s="1" t="inlineStr">
         <is>
-          <t>微弱的</t>
+          <t>昏倒；晕厥；褪色</t>
         </is>
       </c>
       <c r="E2215" s="1" t="inlineStr">
@@ -71171,7 +71315,7 @@
       </c>
       <c r="B2216" s="1" t="inlineStr">
         <is>
-          <t>[iz.maˈɡa(ʁ)] 暗恋&lt;动&gt;</t>
+          <t>[iz.maˈɡa(ʁ)] 压碎；压扁；粉碎&lt;动&gt;</t>
         </is>
       </c>
       <c r="C2216" s="1" t="inlineStr">
@@ -71181,7 +71325,7 @@
       </c>
       <c r="D2216" s="1" t="inlineStr">
         <is>
-          <t>暗恋</t>
+          <t>压碎；压扁；粉碎</t>
         </is>
       </c>
       <c r="E2216" s="1" t="inlineStr">
@@ -71459,7 +71603,7 @@
       </c>
       <c r="B2225" s="1" t="inlineStr">
         <is>
-          <t>[iˈdo.zu] 老人&lt;名&gt;</t>
+          <t>[/iˈdo.zu/] 年老的&lt;形&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2225" s="1" t="inlineStr">
@@ -71469,7 +71613,7 @@
       </c>
       <c r="D2225" s="1" t="inlineStr">
         <is>
-          <t>老人</t>
+          <t>年老的&lt;形&gt;</t>
         </is>
       </c>
       <c r="E2225" s="1" t="inlineStr">
@@ -71843,7 +71987,7 @@
       </c>
       <c r="B2237" s="1" t="inlineStr">
         <is>
-          <t>[kõˈde.sɐ] 伯爵夫人&lt;名&gt;</t>
+          <t>[/kõˈde.sɐ/] 女伯爵&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2237" s="1" t="inlineStr">
@@ -71853,7 +71997,7 @@
       </c>
       <c r="D2237" s="1" t="inlineStr">
         <is>
-          <t>伯爵夫人</t>
+          <t>女伯爵&lt;名&gt;</t>
         </is>
       </c>
       <c r="E2237" s="1" t="inlineStr">
@@ -71907,7 +72051,7 @@
       </c>
       <c r="B2239" s="1" t="inlineStr">
         <is>
-          <t>[ɡaˈta(ʁ)] 猫&lt;动&gt;</t>
+          <t>[ɡaˈta(ʁ)] 偷窃；勾引&lt;动&gt;</t>
         </is>
       </c>
       <c r="C2239" s="1" t="inlineStr">
@@ -71917,7 +72061,7 @@
       </c>
       <c r="D2239" s="1" t="inlineStr">
         <is>
-          <t>猫</t>
+          <t>偷窃；勾引</t>
         </is>
       </c>
       <c r="E2239" s="1" t="inlineStr">
@@ -72003,7 +72147,7 @@
       </c>
       <c r="B2242" s="1" t="inlineStr">
         <is>
-          <t>[is.taˈd͡ʒi.ɐ] 留下来&lt;名&gt;</t>
+          <t>[is.taˈd͡ʒi.ɐ] 逗留；停留；住宿&lt;名&gt;</t>
         </is>
       </c>
       <c r="C2242" s="1" t="inlineStr">
@@ -72013,7 +72157,7 @@
       </c>
       <c r="D2242" s="1" t="inlineStr">
         <is>
-          <t>留下来</t>
+          <t>逗留；停留；住宿</t>
         </is>
       </c>
       <c r="E2242" s="1" t="inlineStr">
@@ -72968,7 +73112,7 @@
       </c>
       <c r="C2272" s="1" t="inlineStr">
         <is>
-          <t>to.ˈma.ɾãʊ̃</t>
+          <t>/to.ˈma.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D2272" s="1" t="inlineStr">
@@ -73059,17 +73203,17 @@
       </c>
       <c r="B2275" s="1" t="inlineStr">
         <is>
-          <t>[fo.ˈsẽ.mʊs] 我们是&lt;动&gt;</t>
+          <t>[fo.ˈsẽ.mʊs] 我们是；我们曾是&lt;动&gt;</t>
         </is>
       </c>
       <c r="C2275" s="1" t="inlineStr">
         <is>
-          <t>fo.ˈsẽ.mʊs</t>
+          <t>/fo.ˈsẽ.mʊs/</t>
         </is>
       </c>
       <c r="D2275" s="1" t="inlineStr">
         <is>
-          <t>我们是</t>
+          <t>我们是；我们曾是</t>
         </is>
       </c>
       <c r="E2275" s="1" t="inlineStr">
@@ -73155,7 +73299,7 @@
       </c>
       <c r="B2278" s="1" t="inlineStr">
         <is>
-          <t>[ˈmi] 我&lt;名&gt;</t>
+          <t>[ˈmi] 唱名米；E音&lt;名&gt;</t>
         </is>
       </c>
       <c r="C2278" s="1" t="inlineStr">
@@ -73165,7 +73309,7 @@
       </c>
       <c r="D2278" s="1" t="inlineStr">
         <is>
-          <t>我</t>
+          <t>唱名米；E音</t>
         </is>
       </c>
       <c r="E2278" s="1" t="inlineStr">
@@ -74022,7 +74166,11 @@
           <t>脱衣舞娘&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C2305" s="1" t="inlineStr"/>
+      <c r="C2305" s="1" t="inlineStr">
+        <is>
+          <t>/ˈstʁɪ.pə(ʁ)/</t>
+        </is>
+      </c>
       <c r="D2305" s="1" t="inlineStr">
         <is>
           <t>脱衣舞娘</t>
@@ -74052,7 +74200,7 @@
       </c>
       <c r="C2306" s="1" t="inlineStr">
         <is>
-          <t>es.ko.ˈʎe.ɾãʊ̃</t>
+          <t>/es.ko.ˈʎe.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D2306" s="1" t="inlineStr">
@@ -74111,7 +74259,7 @@
       </c>
       <c r="B2308" s="1" t="inlineStr">
         <is>
-          <t>[ˈblu.zɐ] 衬衫&lt;名&gt;</t>
+          <t>[/ˈblu.zɐ/] 女式衬衫，罩衫&lt;名&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2308" s="1" t="inlineStr">
@@ -74121,7 +74269,7 @@
       </c>
       <c r="D2308" s="1" t="inlineStr">
         <is>
-          <t>衬衫</t>
+          <t>女式衬衫，罩衫&lt;名&gt;</t>
         </is>
       </c>
       <c r="E2308" s="1" t="inlineStr">
@@ -74175,7 +74323,7 @@
       </c>
       <c r="B2310" s="1" t="inlineStr">
         <is>
-          <t>[ˈfi] 菲&lt;名&gt;</t>
+          <t>[/ˈfi/] 信仰；信心&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2310" s="1" t="inlineStr">
@@ -74185,7 +74333,7 @@
       </c>
       <c r="D2310" s="1" t="inlineStr">
         <is>
-          <t>菲</t>
+          <t>信仰；信心</t>
         </is>
       </c>
       <c r="E2310" s="1" t="inlineStr">
@@ -74306,7 +74454,11 @@
           <t>夜间活动的&lt;形&gt;</t>
         </is>
       </c>
-      <c r="C2314" s="1" t="inlineStr"/>
+      <c r="C2314" s="1" t="inlineStr">
+        <is>
+          <t>/ˈnɔk.tuʁ.nu/</t>
+        </is>
+      </c>
       <c r="D2314" s="1" t="inlineStr">
         <is>
           <t>夜间活动的</t>
@@ -74523,7 +74675,7 @@
       </c>
       <c r="B2321" s="1" t="inlineStr">
         <is>
-          <t>[ẽ.foʁˈka(ʁ)] 挂&lt;动&gt;</t>
+          <t>[ẽ.foʁˈka(ʁ)] 绞死；吊死；悬挂&lt;动&gt;</t>
         </is>
       </c>
       <c r="C2321" s="1" t="inlineStr">
@@ -74533,7 +74685,7 @@
       </c>
       <c r="D2321" s="1" t="inlineStr">
         <is>
-          <t>挂</t>
+          <t>绞死；吊死；悬挂</t>
         </is>
       </c>
       <c r="E2321" s="1" t="inlineStr">
@@ -74555,7 +74707,7 @@
       </c>
       <c r="B2322" s="1" t="inlineStr">
         <is>
-          <t>[tẽ.taˈt͡ʃi.vu] 暂定的&lt;形&gt;</t>
+          <t>[/tẽ.taˈt͡ʃi.vu/] 尝试&lt;adj&gt;</t>
         </is>
       </c>
       <c r="C2322" s="1" t="inlineStr">
@@ -74565,7 +74717,7 @@
       </c>
       <c r="D2322" s="1" t="inlineStr">
         <is>
-          <t>暂定的</t>
+          <t>尝试</t>
         </is>
       </c>
       <c r="E2322" s="1" t="inlineStr">
@@ -74619,7 +74771,7 @@
       </c>
       <c r="B2324" s="1" t="inlineStr">
         <is>
-          <t>[ˈkej.zi] 案例&lt;名&gt;</t>
+          <t>[/ˈkej.zi/] 情况；案例；事例&lt;名&gt;</t>
         </is>
       </c>
       <c r="C2324" s="1" t="inlineStr">
@@ -74629,7 +74781,7 @@
       </c>
       <c r="D2324" s="1" t="inlineStr">
         <is>
-          <t>案例</t>
+          <t>情况；案例；事例</t>
         </is>
       </c>
       <c r="E2324" s="1" t="inlineStr">
@@ -74715,7 +74867,7 @@
       </c>
       <c r="B2327" s="1" t="inlineStr">
         <is>
-          <t>[a.fũˈda(ʁ)] 水槽&lt;动&gt;</t>
+          <t>[a.fũˈda(ʁ)] 下沉；使沉没&lt;动&gt;</t>
         </is>
       </c>
       <c r="C2327" s="1" t="inlineStr">
@@ -74725,7 +74877,7 @@
       </c>
       <c r="D2327" s="1" t="inlineStr">
         <is>
-          <t>水槽</t>
+          <t>下沉；使沉没</t>
         </is>
       </c>
       <c r="E2327" s="1" t="inlineStr">
@@ -74784,7 +74936,7 @@
       </c>
       <c r="C2329" s="1" t="inlineStr">
         <is>
-          <t>a.ni.ˈmax</t>
+          <t>/a.ni.ˈmax/</t>
         </is>
       </c>
       <c r="D2329" s="1" t="inlineStr">
@@ -74910,7 +75062,11 @@
           <t>华盛顿特区&lt;副&gt;</t>
         </is>
       </c>
-      <c r="C2333" s="1" t="inlineStr"/>
+      <c r="C2333" s="1" t="inlineStr">
+        <is>
+          <t>/deˈse/</t>
+        </is>
+      </c>
       <c r="D2333" s="1" t="inlineStr">
         <is>
           <t>华盛顿特区</t>
@@ -74967,7 +75123,7 @@
       </c>
       <c r="B2335" s="1" t="inlineStr">
         <is>
-          <t>[pɾiˈma.ɾjɐ] 小学&lt;名&gt;</t>
+          <t>[/pɾiˈma.ɾjɐ/] 初等的，小学的&lt;形&gt;&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2335" s="1" t="inlineStr">
@@ -74977,7 +75133,7 @@
       </c>
       <c r="D2335" s="1" t="inlineStr">
         <is>
-          <t>小学</t>
+          <t>初等的，小学的&lt;形&gt;</t>
         </is>
       </c>
       <c r="E2335" s="1" t="inlineStr">
@@ -75543,7 +75699,7 @@
       </c>
       <c r="B2353" s="1" t="inlineStr">
         <is>
-          <t>[a.li.mẽ.taˈsɐ̃w̃] 食物&lt;名&gt;</t>
+          <t>[/a.li.mẽ.taˈsɐ̃w̃/] 进食；营养；饮食&lt;noun&gt;</t>
         </is>
       </c>
       <c r="C2353" s="1" t="inlineStr">
@@ -75553,7 +75709,7 @@
       </c>
       <c r="D2353" s="1" t="inlineStr">
         <is>
-          <t>食物</t>
+          <t>进食；营养；饮食</t>
         </is>
       </c>
       <c r="E2353" s="1" t="inlineStr">
@@ -75639,7 +75795,7 @@
       </c>
       <c r="B2356" s="1" t="inlineStr">
         <is>
-          <t>[ˈfɾe(j).ɾi] 弗莱雷&lt;名&gt;</t>
+          <t>[ˈfɾe(j).ɾi] 修士；僧侣&lt;名&gt;</t>
         </is>
       </c>
       <c r="C2356" s="1" t="inlineStr">
@@ -75649,7 +75805,7 @@
       </c>
       <c r="D2356" s="1" t="inlineStr">
         <is>
-          <t>弗莱雷</t>
+          <t>修士；僧侣</t>
         </is>
       </c>
       <c r="E2356" s="1" t="inlineStr">
@@ -75708,7 +75864,7 @@
       </c>
       <c r="C2358" s="1" t="inlineStr">
         <is>
-          <t>ne.ga.ˈtʃi.və</t>
+          <t>/ne.ga.ˈtʃi.və/</t>
         </is>
       </c>
       <c r="D2358" s="1" t="inlineStr">
@@ -75836,7 +75992,7 @@
       </c>
       <c r="C2362" s="1" t="inlineStr">
         <is>
-          <t>gos.ˈta.ɾãʊ̃</t>
+          <t>/gos.ˈta.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D2362" s="1" t="inlineStr">
@@ -75898,10 +76054,14 @@
           <t>党卫军；党卫队&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C2364" s="1" t="inlineStr"/>
+      <c r="C2364" s="1" t="inlineStr">
+        <is>
+          <t>/ss/</t>
+        </is>
+      </c>
       <c r="D2364" s="1" t="inlineStr">
         <is>
-          <t>党卫军</t>
+          <t>党卫军；党卫队</t>
         </is>
       </c>
       <c r="E2364" s="1" t="inlineStr">
@@ -76179,7 +76339,7 @@
       </c>
       <c r="B2373" s="1" t="inlineStr">
         <is>
-          <t>[kɾu.zaˈmẽ.tu] 穿越&lt;名&gt;</t>
+          <t>[kɾu.zaˈmẽ.tu] 十字路口；交叉；杂交&lt;名&gt;</t>
         </is>
       </c>
       <c r="C2373" s="1" t="inlineStr">
@@ -76189,7 +76349,7 @@
       </c>
       <c r="D2373" s="1" t="inlineStr">
         <is>
-          <t>穿越</t>
+          <t>十字路口；交叉；杂交</t>
         </is>
       </c>
       <c r="E2373" s="1" t="inlineStr">
@@ -76307,7 +76467,7 @@
       </c>
       <c r="B2377" s="1" t="inlineStr">
         <is>
-          <t>[kiˈzɛ.ɾɐ̃w̃] 通缉&lt;动&gt;</t>
+          <t>[kiˈzɛ.ɾɐ̃w̃] 想要；愿意&lt;动&gt;</t>
         </is>
       </c>
       <c r="C2377" s="1" t="inlineStr">
@@ -76317,7 +76477,7 @@
       </c>
       <c r="D2377" s="1" t="inlineStr">
         <is>
-          <t>通缉</t>
+          <t>想要；愿意</t>
         </is>
       </c>
       <c r="E2377" s="1" t="inlineStr">
@@ -76342,7 +76502,11 @@
           <t>美丽的&lt;形&gt;</t>
         </is>
       </c>
-      <c r="C2378" s="1" t="inlineStr"/>
+      <c r="C2378" s="1" t="inlineStr">
+        <is>
+          <t>/bˈello/</t>
+        </is>
+      </c>
       <c r="D2378" s="1" t="inlineStr">
         <is>
           <t>美丽的</t>
@@ -76367,7 +76531,7 @@
       </c>
       <c r="B2379" s="1" t="inlineStr">
         <is>
-          <t>[neˈva.dɐ] 内华达州&lt;名&gt;</t>
+          <t>[neˈva.dɐ] 降雪；大雪&lt;名&gt;</t>
         </is>
       </c>
       <c r="C2379" s="1" t="inlineStr">
@@ -76377,7 +76541,7 @@
       </c>
       <c r="D2379" s="1" t="inlineStr">
         <is>
-          <t>内华达州</t>
+          <t>降雪；大雪</t>
         </is>
       </c>
       <c r="E2379" s="1" t="inlineStr">
@@ -77172,7 +77336,7 @@
       </c>
       <c r="C2404" s="1" t="inlineStr">
         <is>
-          <t>pɾẽ.ˈde.ɾãʊ̃</t>
+          <t>/pɾẽ.ˈde.ɾãʊ̃/</t>
         </is>
       </c>
       <c r="D2404" s="1" t="inlineStr">
@@ -77362,7 +77526,11 @@
           <t>日落&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C2410" s="1" t="inlineStr"/>
+      <c r="C2410" s="1" t="inlineStr">
+        <is>
+          <t>/ˌpoʁ du ˈsɔw/</t>
+        </is>
+      </c>
       <c r="D2410" s="1" t="inlineStr">
         <is>
           <t>日落</t>
@@ -77579,7 +77747,7 @@
       </c>
       <c r="B2417" s="1" t="inlineStr">
         <is>
-          <t>[ˈta.ki] 塔克&lt;名&gt;</t>
+          <t>[ˈta.ki] 啪嗒声&lt;名&gt;</t>
         </is>
       </c>
       <c r="C2417" s="1" t="inlineStr">
@@ -77589,7 +77757,7 @@
       </c>
       <c r="D2417" s="1" t="inlineStr">
         <is>
-          <t>塔克</t>
+          <t>啪嗒声</t>
         </is>
       </c>
       <c r="E2417" s="1" t="inlineStr">
@@ -77646,7 +77814,11 @@
           <t>杜松子酒&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C2419" s="1" t="inlineStr"/>
+      <c r="C2419" s="1" t="inlineStr">
+        <is>
+          <t>/ˈd͡ʒin/</t>
+        </is>
+      </c>
       <c r="D2419" s="1" t="inlineStr">
         <is>
           <t>杜松子酒</t>
@@ -78119,17 +78291,17 @@
       </c>
       <c r="B2434" s="1" t="inlineStr">
         <is>
-          <t>[ˈtʊʊ] 头&lt;动&gt;</t>
+          <t>[ˈtʊʊ] 我在；我是&lt;动&gt;</t>
         </is>
       </c>
       <c r="C2434" s="1" t="inlineStr">
         <is>
-          <t>ˈtʊʊ</t>
+          <t>/ˈtʊʊ/</t>
         </is>
       </c>
       <c r="D2434" s="1" t="inlineStr">
         <is>
-          <t>头</t>
+          <t>我在；我是</t>
         </is>
       </c>
       <c r="E2434" s="1" t="inlineStr">
@@ -78183,7 +78355,7 @@
       </c>
       <c r="B2436" s="1" t="inlineStr">
         <is>
-          <t>[ẽ.ve.neˈna(ʁ)] 毒药&lt;动&gt;</t>
+          <t>[ẽ.ve.neˈna(ʁ)] 毒害；使中毒；下毒&lt;动&gt;</t>
         </is>
       </c>
       <c r="C2436" s="1" t="inlineStr">
@@ -78193,7 +78365,7 @@
       </c>
       <c r="D2436" s="1" t="inlineStr">
         <is>
-          <t>毒药</t>
+          <t>毒害；使中毒；下毒</t>
         </is>
       </c>
       <c r="E2436" s="1" t="inlineStr">
@@ -78215,7 +78387,7 @@
       </c>
       <c r="B2437" s="1" t="inlineStr">
         <is>
-          <t>[ˈaw] 哇&lt;叹&gt;</t>
+          <t>[ˈaw] 汪汪；哎哟&lt;叹&gt;</t>
         </is>
       </c>
       <c r="C2437" s="1" t="inlineStr">
@@ -78225,7 +78397,7 @@
       </c>
       <c r="D2437" s="1" t="inlineStr">
         <is>
-          <t>哇</t>
+          <t>汪汪；哎哟</t>
         </is>
       </c>
       <c r="E2437" s="1" t="inlineStr">
@@ -78343,7 +78515,7 @@
       </c>
       <c r="B2441" s="1" t="inlineStr">
         <is>
-          <t>[isˈta.kɐ] 股份&lt;名&gt;</t>
+          <t>[isˈta.kɐ] 木桩；桩&lt;名&gt;</t>
         </is>
       </c>
       <c r="C2441" s="1" t="inlineStr">
@@ -78353,7 +78525,7 @@
       </c>
       <c r="D2441" s="1" t="inlineStr">
         <is>
-          <t>股份</t>
+          <t>木桩；桩</t>
         </is>
       </c>
       <c r="E2441" s="1" t="inlineStr">
@@ -78380,7 +78552,7 @@
       </c>
       <c r="C2442" s="1" t="inlineStr">
         <is>
-          <t>a.tɾa.ˈsãʊ̃</t>
+          <t>/a.tɾa.ˈsãʊ̃/</t>
         </is>
       </c>
       <c r="D2442" s="1" t="inlineStr">
@@ -79111,7 +79283,7 @@
       </c>
       <c r="B2465" s="1" t="inlineStr">
         <is>
-          <t>[a.ʁɐ̃ˈɲɐ̃w̃] 从头开始&lt;名&gt;</t>
+          <t>[a.ʁɐ̃ˈɲɐ̃w̃] 划痕；抓痕&lt;名&gt;</t>
         </is>
       </c>
       <c r="C2465" s="1" t="inlineStr">
@@ -79121,7 +79293,7 @@
       </c>
       <c r="D2465" s="1" t="inlineStr">
         <is>
-          <t>从头开始</t>
+          <t>划痕；抓痕</t>
         </is>
       </c>
       <c r="E2465" s="1" t="inlineStr">
@@ -79402,7 +79574,11 @@
           <t>克林贡语&lt;名&gt;</t>
         </is>
       </c>
-      <c r="C2474" s="1" t="inlineStr"/>
+      <c r="C2474" s="1" t="inlineStr">
+        <is>
+          <t>/klˈinɡon/</t>
+        </is>
+      </c>
       <c r="D2474" s="1" t="inlineStr">
         <is>
           <t>克林贡语</t>
@@ -79496,7 +79672,7 @@
       </c>
       <c r="C2477" s="1" t="inlineStr">
         <is>
-          <t>ko.xe.ˈsãʊ̃</t>
+          <t>/ko.xe.ˈsãʊ̃/</t>
         </is>
       </c>
       <c r="D2477" s="1" t="inlineStr">
@@ -79875,7 +80051,7 @@
       </c>
       <c r="B2489" s="1" t="inlineStr">
         <is>
-          <t>[ˈpɔʁ.kɐ] 坚果&lt;名&gt;</t>
+          <t>[ˈpɔʁ.kɐ] 螺母；母猪&lt;名&gt;</t>
         </is>
       </c>
       <c r="C2489" s="1" t="inlineStr">
@@ -79885,7 +80061,7 @@
       </c>
       <c r="D2489" s="1" t="inlineStr">
         <is>
-          <t>坚果</t>
+          <t>螺母；母猪</t>
         </is>
       </c>
       <c r="E2489" s="1" t="inlineStr">
@@ -80003,7 +80179,7 @@
       </c>
       <c r="B2493" s="1" t="inlineStr">
         <is>
-          <t>[pɾe.zi.dẽ.siˈaw] 总统&lt;形&gt;</t>
+          <t>[pɾe.zi.dẽ.siˈaw] 总统的&lt;形&gt;</t>
         </is>
       </c>
       <c r="C2493" s="1" t="inlineStr">
@@ -80013,7 +80189,7 @@
       </c>
       <c r="D2493" s="1" t="inlineStr">
         <is>
-          <t>总统</t>
+          <t>总统的</t>
         </is>
       </c>
       <c r="E2493" s="1" t="inlineStr">
@@ -80099,7 +80275,7 @@
       </c>
       <c r="B2496" s="1" t="inlineStr">
         <is>
-          <t>[ˈmɔ.vew] 移动&lt;名&gt;</t>
+          <t>[ˈmɔ.vew] 家具；可移动的&lt;名&gt;</t>
         </is>
       </c>
       <c r="C2496" s="1" t="inlineStr">
@@ -80109,7 +80285,7 @@
       </c>
       <c r="D2496" s="1" t="inlineStr">
         <is>
-          <t>移动</t>
+          <t>家具；可移动的</t>
         </is>
       </c>
       <c r="E2496" s="1" t="inlineStr">
